--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=8 … hard=5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2227,11 +2227,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>easy=5 … hard=10</t>
+          <t>easy=6 … hard=14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2265,11 +2265,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>easy=3 … hard=2</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=0.05 … hard=0.08</t>
+          <t>easy=0.03 … hard=0.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2759,11 +2759,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=8 … hard=4</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2797,11 +2797,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=6 … hard=3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=6 … hard=3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2864,20 +2864,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>prawo_kara_brak_garnizonu</t>
+          <t>prawo_palac</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
+          <t>Pałac — główne źródło Prawa (≈1,75× jednostka garnizonu; PT 2026-07).</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2</v>
+        <v>35</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=45 … hard=28</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2902,20 +2902,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada</t>
+          <t>prawo_kara_brak_garnizonu</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa dla małej osady (D18-6=A).</t>
+          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2940,25 +2940,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada_prog</t>
+          <t>prawo_bonus_osada</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+          <t>LEGACY — zastąpione przez prawo_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=4 … hard=4</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>pkt Prawa</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2978,33 +2978,111 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>prawo_bonus_osiedle_pop</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>D-START-OSIEDLE: bonus Prawa pop 1→4. Cel PorPct T1 pop=1: easy ~75%, normal ~55%, hard ~35% (kult+rel).</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>28, 20, 14, 8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>easy=[32, 24, 16, 10] … hard=[22, 16, 10, 6]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osada_prog</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>prawo_bonus_stolica_easy</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>easy=1 … hard=0</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>pkt Prawa</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Prawo, garnizon</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>
@@ -3943,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4135,19 +4213,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kamieniarski</t>
+          <t>mielerz</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Warsztat kamieniarski</t>
+          <t>Mielerz</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -4202,57 +4280,57 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Murarstwo</t>
+          <t>Obróbka drewna</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kuznia</t>
+          <t>kamieniarski</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuznia</t>
+          <t>Warsztat kamieniarski</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
@@ -4272,101 +4350,101 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Brązownictwo</t>
+          <t>Murarstwo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>targowisko</t>
+          <t>kuznia</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Targowisko (Rynek)</t>
+          <t>Kuznia</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>2</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Wymiana</t>
+          <t>Brązownictwo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>odlewnia_brazu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Port handlowy</t>
+          <t>Piec hutniczy</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -4375,10 +4453,10 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4399,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -4424,35 +4502,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Żegluga</t>
+          <t>Brązownictwo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>karawanseraj</t>
+          <t>odlewnia_zelaza</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Karawanseraj</t>
+          <t>Odlewnia żelaza</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4470,13 +4548,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -4494,30 +4572,30 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Handel</t>
+          <t>Obróbka żelaza</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>spichlerz</t>
+          <t>targowisko</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spichlerz</t>
+          <t>Targowisko (Rynek)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4526,34 +4604,34 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -4568,39 +4646,39 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Wymiana</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>swiatynia</t>
+          <t>port</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiatynia</t>
+          <t>Port handlowy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4609,10 +4687,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -4624,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -4633,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -4646,44 +4724,44 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Mistycyzm</t>
+          <t>Żegluga</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>biblioteka</t>
+          <t>port_wielki</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Biblioteka</t>
+          <t>Port wielki</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -4698,16 +4776,16 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -4720,35 +4798,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Inżynieria</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>studnia</t>
+          <t>karawanseraj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Studnia</t>
+          <t>Karawanseraj</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -4760,19 +4838,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -4784,49 +4862,49 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Gospodarka wodna</t>
+          <t>Handel</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mury</t>
+          <t>spichlerz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mury</t>
+          <t>Spichlerz</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -4837,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -4849,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -4861,64 +4939,64 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Budownictwo</t>
+          <t>Garncarstwo</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>koszary</t>
+          <t>garncarnia</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Koszary</t>
+          <t>Garncarnia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
@@ -4938,39 +5016,39 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Wojskowosc</t>
+          <t>Garncarstwo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>magazyn</t>
+          <t>cegielnia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Magazyn</t>
+          <t>Cegielnia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4991,10 +5069,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -5016,29 +5094,29 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Handel</t>
+          <t>Garncarstwo</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stela</t>
+          <t>kamienne_kregi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Stela / Pomnik</t>
+          <t>Kamienne kręgi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -5056,7 +5134,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -5080,7 +5158,7 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -5090,29 +5168,29 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Murarstwo</t>
+          <t>Mistycyzm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>palac</t>
+          <t>swiatynia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Palac</t>
+          <t>Świątynia</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -5130,13 +5208,13 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5154,7 +5232,7 @@
         <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -5162,67 +5240,71 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Religia</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kuznia_zelaza</t>
+          <t>biblioteka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kuźnia żelaza</t>
+          <t>Biblioteka</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -5230,39 +5312,39 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Obróbka żelaza</t>
+          <t>Pismo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wielka_kuznia</t>
+          <t>studnia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia</t>
+          <t>Studnia</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -5274,19 +5356,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -5298,39 +5380,39 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Hutnictwo żelaza</t>
+          <t>Gospodarka wodna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fort</t>
+          <t>akwedukt</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fort</t>
+          <t>Akwedukt</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -5348,10 +5430,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -5372,70 +5454,70 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Inżynieria</t>
+          <t>Budownictwo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>warsztat_oblezniczy</t>
+          <t>mennica</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Warsztat oblężniczy</t>
+          <t>Mennica</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>10</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
@@ -5452,110 +5534,110 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Oblężnictwo</t>
+          <t>Waluta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>akademia</t>
+          <t>mury</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Akademia</t>
+          <t>Mury</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>10</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Filozofia</t>
+          <t>Budownictwo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>teatr</t>
+          <t>koszary</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Teatr</t>
+          <t>Koszary</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5567,19 +5649,19 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5591,48 +5673,48 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Filozofia</t>
+          <t>Wojskowosc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>magazyn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sąd</t>
+          <t>Magazyn</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -5641,19 +5723,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -5665,10 +5747,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -5678,35 +5760,35 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Kodeks prawa</t>
+          <t>Handel</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pretorium</t>
+          <t>stela</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pretorium</t>
+          <t>Stela / Pomnik</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -5715,60 +5797,60 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Kodeks prawa</t>
+          <t>Murarstwo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>laznia_publiczna</t>
+          <t>palac</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Łaźnia publiczna</t>
+          <t>Palac</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D25" t="n">
         <v>12</v>
@@ -5783,37 +5865,37 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -5824,99 +5906,95 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Medycyna</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lazaret</t>
+          <t>kuznia_zelaza</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lazaret</t>
+          <t>Kuźnia żelaza</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Medycyna</t>
+          <t>Obróbka żelaza</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>akademia_wojskowa</t>
+          <t>wielka_kuznia</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akademia wojskowa</t>
+          <t>Wielka Kuźnia</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
@@ -5925,54 +6003,720 @@
         <v>4</v>
       </c>
       <c r="F27" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>23</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>7</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hutnictwo żelaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fort</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cytadela</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Inżynieria</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>warsztat_oblezniczy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Warsztat oblężniczy</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Oblężnictwo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>akademia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Akademia</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>70</v>
+      </c>
+      <c r="D30" t="n">
         <v>15</v>
       </c>
-      <c r="N27" t="n">
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>10</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4</v>
+      </c>
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Filozofia</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>teatr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Teatr</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>55</v>
+      </c>
+      <c r="D31" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Filozofia</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sąd</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>55</v>
+      </c>
+      <c r="D32" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Kodeks prawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pretorium</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pretorium</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Kodeks prawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>laznia_publiczna</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Łaźnia publiczna</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>50</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medycyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>lazaret</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lazaret</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>55</v>
+      </c>
+      <c r="D35" t="n">
+        <v>12</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medycyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>akademia_wojskowa</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Akademia wojskowa</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>80</v>
+      </c>
+      <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="n">
         <v>4</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>Sztuka wojenna</t>
         </is>
@@ -6468,7 +7212,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Stolarnia</t>
+          <t>Stolarnia, Mielerz</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6511,7 +7255,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Spichlerz</t>
+          <t>Spichlerz; Garncarnia; Cegielnia</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -6590,12 +7334,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B1-Q2A Maciej 2026-06-29</t>
+          <t>B1-Q2A Maciej 2026-06-29; T-TECH-4: Tarasy po Rolnictwie</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Farma</t>
+          <t>Farma, Tarasy uprawne</t>
         </is>
       </c>
     </row>
@@ -6724,12 +7468,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Swiatynia</t>
+          <t>Kamienne kręgi</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>10</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>T-TECH-8: pierwszy poziom kultu — upgrade do Świątyni po Religii</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6861,7 +7610,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kuznia; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Falanga, Hastati, Kusznik, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Wojownik celtycki, Gaesatae, Wojownik germański, Berserker germański, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
+          <t>Odlewnia brązu; Kuznia; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Falanga, Hastati, Kusznik, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Gaesatae, Soldurii, Wojownik germański, Berserker germański, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -6869,7 +7618,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kończy Epokę 1</t>
+          <t>kończy Epokę 1; ABC-7: Popalnia brązu na mapie</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Popalnia brązu</t>
         </is>
       </c>
     </row>
@@ -6983,9 +7737,19 @@
           <t>Garncarstwo</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Świątynia (upgrade kręgów)</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>48</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>T-TECH-8: upgrade kamienne_kregi → swiatynia (suma bonusów w JSON)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7163,12 +7927,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Mury</t>
+          <t>Mury; Akwedukt</t>
         </is>
       </c>
       <c r="I22" t="n">
         <v>85</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>T-TECH-6: Akwedukt v1.0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7194,12 +7963,17 @@
           <t>Handel + Matematyka</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Mennica</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>100</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>kończy Epokę 2 (Pieniądz)</t>
+          <t>kończy Epokę 2 (Pieniądz); T-TECH-6: Mennica v1.0</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7998,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Huta</t>
+          <t>Odlewnia brązu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7247,7 +8021,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>kończy Epokę 2 / otwiera Epokę 3; jednostki żelazne (Wojownik celtycki, Wojownik germański itp.) — do zdefiniowania przez UNITS; Kuźnia żelaza = NOWY budynek dla EKONOMIA</t>
+          <t>kończy Epokę 2 / otwiera Epokę 3; jednostki żelazne (Gaesatae, Soldurii, Wojownik germański itp.) — do zdefiniowania przez UNITS; Kuźnia żelaza = NOWY budynek dla EKONOMIA</t>
         </is>
       </c>
     </row>
@@ -7396,7 +8170,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Drogi żelazne</t>
+          <t>Drogi brukowane</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7407,14 +8181,9 @@
       <c r="C29" t="n">
         <v>7</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>żelazo</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inżynieria + Obróbka żelaza</t>
+          <t>Inżynieria + Budownictwo</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -7422,7 +8191,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Drogi brukowane = NOWE ulepszenie terenu dla DANE/MAPA (+ruch, +handel między miastami); bonus +pieniądz na szlakach handlowych</t>
+          <t>T-TECH-9: ulepszenie Droga brukowana (+2 ruch, upgrade z Drogi)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Droga brukowana</t>
         </is>
       </c>
     </row>
@@ -8470,7 +9244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8536,15 +9310,15 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Próg wzrostu populacji: Próg(N) = 10 + N × wartość. Większy = wolniejszy wzrost. [PT]</t>
+          <t>Próg wzrostu populacji: Próg(N) = 20 + N × wartość. Większy = wolniejszy wzrost. Maciej 2026-07-09: 2× żywność do wzrostu (baza 10→20 w kodzie + wsp. podwojone easy/normal/hard). [PT]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>easy=6 … hard=10</t>
+          <t>easy=12 … hard=20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8574,7 +9348,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ułamek żywności zachowany w Spichlerzu po awansie populacji (0.50 = 50%). [PT]</t>
+          <t>Ze Spichlerzem w mieście: ułamek bufora wzrostu zachowany po awansie populacji (+1). Bez Spichlerza bufor zeruje się. Maciej 2026-07-06: normal=50%.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -8582,7 +9356,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>easy=0.62 … hard=0.38</t>
+          <t>easy=0.6 … hard=0.4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -8607,25 +9381,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>akwedukt_prog_ludnosci</t>
+          <t>handel_surowiec_min_stock</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Max populacja bez Akweduktu. Po jego budowie blokada zdjęta. [PT]</t>
+          <t>ABC-15 Maciej 2026-07-04: handel surowcem dopiero gdy stock ≥ wartość; 1 szt. zostaje = dostęp (v2 handlu).</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>easy=8 … hard=4</t>
+          <t>easy=2 … hard=2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ludność</t>
+          <t>szt.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -8645,25 +9419,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>zywnosc_zuzytka_populacja</t>
+          <t>akwedukt_prog_ludnosci</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Zużycie żywności na 1 punkt populacji na turę.</t>
+          <t>Max populacja bez Akweduktu (Maciej: normal=5). Wzrost zablokowany przy cap — nadwyżka żywności idzie do armii lub przepada (B5). [PT]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>żywność/turę/os.</t>
+          <t>ludność</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -8683,25 +9457,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zywnosc_jednostka_ruch</t>
+          <t>akwedukt_max_ludnosci</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Zużycie żywności jednostki wojskowej w ruchu lub w garnizonie.</t>
+          <t>Twardy cap populacji Z Akweduktem (Maciej 2026-07-07: normal=15). Epoka 4+ — osobny unlock (do decyzji ABC).</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=15 … hard=15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>żywność/turę</t>
+          <t>ludność</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -8721,25 +9495,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zywnosc_jednostka_oboz</t>
+          <t>zywnosc_zuzytka_populacja</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Zużycie żywności jednostki wojskowej obozującej (bez ruchu).</t>
+          <t>Zużycie żywności na 1 punkt populacji na turę.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>easy=0.38 … hard=0.62</t>
+          <t>easy=1 … hard=2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>żywność/turę</t>
+          <t>żywność/turę/os.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -8759,25 +9533,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>suwak_handel_nauka_domyslnie</t>
+          <t>zywnosc_jednostka_ruch</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Nauka (= BADANIA) w podziale Handlu netto. Default 20% (Maciej 2026-06-25).</t>
+          <t>Zużycie żywności jednostki wojskowej w ruchu lub w garnizonie.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=20 … hard=20</t>
+          <t>easy=1 … hard=2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>żywność/turę</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -8797,25 +9571,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>suwak_handel_pieniadz_domyslnie</t>
+          <t>zywnosc_jednostka_oboz</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Pieniądz (= SKARBIEC/podatek) w podziale Handlu netto. Default 70% (Maciej 2026-06-25).</t>
+          <t>Zużycie żywności jednostki wojskowej obozującej (bez ruchu).</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=70 … hard=70</t>
+          <t>easy=0.38 … hard=0.62</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>żywność/turę</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -8835,20 +9609,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>suwak_handel_luksus_domyslnie</t>
+          <t>suwak_handel_nauka_domyslnie</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Luksus (= WEALTH/rozwój) w podziale Handlu netto. Default 10% (Maciej 2026-06-25).</t>
+          <t>Domyślny udział strumienia Nauka (= BADANIA) w podziale Handlu netto. Default 20% (Maciej 2026-06-25).</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=10 … hard=10</t>
+          <t>easy=20 … hard=20</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8873,12 +9647,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>suwak_praca_budynki_domyslnie</t>
+          <t>suwak_handel_pieniadz_domyslnie</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Praca→Budynki w podziale Pracy netto. [PT]</t>
+          <t>Domyślny udział strumienia Pieniądz (= SKARBIEC/podatek) w podziale Handlu netto. Default 70% (Maciej 2026-06-25).</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -8911,20 +9685,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>suwak_praca_teren_domyslnie</t>
+          <t>suwak_handel_luksus_domyslnie</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Praca→Teren (ulepszenia heksów). [PT]</t>
+          <t>Domyślny udział strumienia Zamożność (Wealth) w podziale Handlu netto. Default 10% (Maciej 2026-06-25). Luksus ≠ surowiec — osobna kategoria elitarna (poza grą v1).</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=30 … hard=30</t>
+          <t>easy=10 … hard=10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8949,12 +9723,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>suwak_zywnosc_rozwoj_domyslnie</t>
+          <t>suwak_praca_budynki_domyslnie</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział brutto żywności imperium → rozwój miast (magazyn/wzrost). Reszta → zapasy państwa. Decyzja Maciej Q1 HUD 2026-06-26.</t>
+          <t>Domyślny udział strumienia Praca→Budynki w podziale Pracy netto. [PT]</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -8962,7 +9736,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=70 … hard=60</t>
+          <t>easy=70 … hard=70</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8987,25 +9761,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>glod_wojska_hp_frac</t>
+          <t>suwak_praca_teren_domyslnie</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Atrycja HP jednostek na mapie gdy zapasy państwa &lt; 0 po koszcie armii (−8% maxHP/tura normal).</t>
+          <t>Domyślny udział strumienia Praca→Teren (ulepszenia heksów). [PT]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.08</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=0.06 … hard=0.1</t>
+          <t>easy=30 … hard=30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ułamek maxHP</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -9025,12 +9799,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>spichlerz_pojemnosc_zapasow_panstwa</t>
+          <t>suwak_zywnosc_rozwoj_domyslnie</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>B5-SP: max zapasów armii na 1 Spichlerz w imperium; suma = wartość × liczba Spichlerzy. Nadwyżka przepada.</t>
+          <t>Domyślny udział brutto żywności imperium → rozwój miast (magazyn/wzrost). Reszta → zapasy państwa. Start gry: 100% wzrost, 0% armia (Maciej 2026-07-03).</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9038,12 +9812,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=120 … hard=80</t>
+          <t>easy=100 … hard=100</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🍞</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -9063,25 +9837,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>korupcja_wspolczynnik_dystansu</t>
+          <t>glod_wojska_hp_frac</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Strata% += Dystans_od_Stolicy × wartość. Im większy, tym dotkliwsza korupcja. [PT]</t>
+          <t>Atrycja HP jednostek na mapie gdy zapasy państwa &lt; 0 po koszcie armii (−8% maxHP/tura normal).</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=1 … hard=3</t>
+          <t>easy=0.06 … hard=0.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>per pole</t>
+          <t>ułamek maxHP</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -9101,25 +9875,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>korupcja_wspolczynnik_miast</t>
+          <t>spichlerz_pojemnosc_zapasow_panstwa</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Strata% += Liczba_Miast × wartość. Każde nowe miasto podnosi korupcję globalnie. [PT]</t>
+          <t>Max zapasów armii na 1 Spichlerz w imperium (100% odkładania). Suma = wartość × liczba Spichlerzy. Bez Spichlerza: odkładanie 50%, bez limitu pojemności.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=120 … hard=80</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>per miasto</t>
+          <t>🍞</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -9139,33 +9913,185 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>armia_odklad_bez_spichlerza</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Od startu gry: ułamek netto żywności armii (po koszcie wojska) odkładany do zapasów państwa BEZ Spichlerza w imperium. Reszta przepada.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>easy=0.6 … hard=0.4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ułamek</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>armia_odklad_ze_spichlerzem</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Ułamek netto żywności armii odkładany do zapasów państwa gdy w imperium jest ≥1 Spichlerz (100%). Limit pojemności = spichlerz_pojemnosc × liczba Spichlerzy.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ułamek</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>korupcja_wspolczynnik_dystansu</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Strata% += Dystans_od_Stolicy × wartość. Im większy, tym dotkliwsza korupcja. [PT]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>per pole</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>korupcja_wspolczynnik_miast</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Strata% += Liczba_Miast × wartość. Każde nowe miasto podnosi korupcję globalnie. [PT]</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>per miasto</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>korupcja_cap</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maksymalna strata z tytułu korupcji/marnotrawstwa (cap = 50%). [PT]</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D22" t="n">
         <v>50</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>easy=38 … hard=62</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>turn-economy, HUD suwaki</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -10560,7 +11486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10849,12 +11775,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ulepszenie_farma_zywnosc</t>
+          <t>teren_las_praca</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Bonus żywności z wybudowanej Farmy na polu (Łąka, Równina). [PT — do strojenia]</t>
+          <t>Bonus Pracy z nakładki Las (dostęp do drewna / wyrąb).</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -10862,12 +11788,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2.5 … hard=1.5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>żywność/turę</t>
+          <t>Praca/turę</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -10887,20 +11813,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ulepszenie_irygacja_zywnosc</t>
+          <t>ulepszenie_farma_zywnosc</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Bonus żywności z Irygacji (lepsze pola uprawne, wymaga tech). [PT — do strojenia]</t>
+          <t>Bonus żywności z wybudowanej Farmy na polu (Łąka, Równina). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10925,25 +11851,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ulepszenie_kopalnia_kamien</t>
+          <t>ulepszenie_irygacja_zywnosc</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Bonus Kamienia z Kopalni na Wzgórzach/Górach (wymaga tech Murarstwo). [PT — do strojenia]</t>
+          <t>Bonus żywności z Irygacji (lepsze pola uprawne, wymaga tech). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kamień/turę</t>
+          <t>żywność/turę</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -10963,25 +11889,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ulepszenie_droga_ruch</t>
+          <t>ulepszenie_kopalnia_kamien</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Bonus szybkości ruchu jednostek na polach z Drogą (skrócenie kosztu ruchu). [PT — do strojenia]</t>
+          <t>Bonus Kamienia z Kopalni na Wzgórzach/Górach (wymaga tech Murarstwo). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>hex/turę bonus</t>
+          <t>Kamień/turę</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -11001,25 +11927,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ulepszenie_pastwisko_bydlo_produkcja</t>
+          <t>ulepszenie_droga_ruch</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik Pracy/produkcji gdy bydło przypisane do Pastwiska (×200%). [PT — do strojenia]</t>
+          <t>Bonus szybkości ruchu jednostek na polach z Drogą (skrócenie kosztu ruchu). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>hex/turę bonus</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -11039,12 +11965,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ulepszenie_pastwisko_owce_zywnosc</t>
+          <t>ulepszenie_pastwisko_bydlo_produkcja</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Bonus żywności gdy owce przypisane do Pastwiska. [PT — do strojenia]</t>
+          <t>Mnożnik Pracy/produkcji gdy bydło przypisane do Pastwiska (×200%). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11057,15 +11983,53 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>okolica, heks bonus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ulepszenie_pastwisko_owce_zywnosc</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bonus żywności gdy owce przypisane do Pastwiska. [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>easy=3 … hard=1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>żywność/turę</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>okolica, heks bonus</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -11082,7 +12046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11338,7 +12302,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Bonus Zdrowia za małe miasto (populacja ≤ próg zagęszczenia). Małe miasto = łatwiejsze zarządzanie sanitarne. [PT]</t>
+          <t>LEGACY — zastąpione przez zdrowie_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11371,25 +12335,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zdrowie_kara_zagęszczenie</t>
+          <t>zdrowie_bonus_osiedle_pop</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za zagęszczenie — odejmuje 1 pkt Zdrowia za każdy punkt populacji powyżej progu zagęszczenia. [PT]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-1</v>
+          <t>D-START-OSIEDLE: bonus Zdrowia malejący pop 1→4 (indeks 0=pop1 … 3=pop4).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2, 1, 1, 0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=[3, 2, 1, 1] … hard=[1, 1, 0, 0]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pkt/1 ludności</t>
+          <t>pkt Zdrowia</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -11409,25 +12375,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zdrowie_prog_zagęszczenia</t>
+          <t>zdrowie_kara_zagęszczenie</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Próg zagęszczenia — poniżej tej liczby mieszkańców kara zagęszczenia NIE jest naliczana. [PT — do strojenia]</t>
+          <t>Kara Zdrowia za zagęszczenie — odejmuje 1 pkt Zdrowia za każdy punkt populacji powyżej progu zagęszczenia. [PT]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ludność</t>
+          <t>pkt/1 ludności</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -11447,25 +12413,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zdrowie_kara_bagno</t>
+          <t>zdrowie_prog_zagęszczenia</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia gdy bagno lub dżungla w promieniu miasta (choroby, komary). [PT]</t>
+          <t>Próg zagęszczenia — poniżej tej liczby mieszkańców kara zagęszczenia NIE jest naliczana. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=5 … hard=3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pkt Zdrowia</t>
+          <t>ludność</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -11485,12 +12451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zdrowie_kara_dzungla</t>
+          <t>zdrowie_kara_bagno</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za dżunglę w pobliżu (wilgoć, choroby tropikalne). [PT — do strojenia]</t>
+          <t>Kara Zdrowia gdy bagno w promieniu okolicy miasta (choroby, komary). Nie dotyczy lasu. [PT]</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -11523,20 +12489,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zdrowie_kara_zanieczyszczenie</t>
+          <t>zdrowie_bonus_las</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Huta, Mielerz itp.). Późne epoki. [PT]</t>
+          <t>Bonus Zdrowia gdy w promieniu okolicy miasta jest co najmniej jeden heks z nakładką Las (świeże powietrze, zasoby leśne). [PT]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -11561,20 +12527,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zdrowie_kara_brak_wody</t>
+          <t>zdrowie_kara_dzungla</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia gdy miasto nie ma dostępu do świeżej wody (brak Rzeki, Studni ani Akweduktu). [PT — do strojenia]</t>
+          <t>REZERWA — kara za prawdziwą dżunglę (osobna nakładka klimatyczna). Nakładka Las używa zdrowie_bonus_las, nie tej kary. [PT]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -11599,25 +12565,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zdrowie_modyfikator_wzrostu</t>
+          <t>zdrowie_kara_zanieczyszczenie</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Modyfikator_Zdrowia = max(0, 1 + Zdrowie × wartość). Np. Zdrowie +4 → ×1,20; Zdrowie −3 → stagnacja. [PT]</t>
+          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Huta, Mielerz itp.). Późne epoki. [PT]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.05</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=0.06 … hard=0.04</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>per pkt Zdrowia</t>
+          <t>pkt Zdrowia</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -11637,20 +12603,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>zdrowie_prog_stagnacja</t>
+          <t>zdrowie_kara_brak_wody</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Gdy Zdrowie ≤ tego progu → wzrost populacji zatrzymany (stagnacja). Wzrost odblokowany dopiero gdy Zdrowie &gt; 0. [PT]</t>
+          <t>Kara Zdrowia gdy miasto nie ma dostępu do świeżej wody (brak Rzeki, Studni ani Akweduktu). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=0 … hard=0</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -11675,25 +12641,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>zdrowie_prog_ubytek_populacji</t>
+          <t>zdrowie_modyfikator_wzrostu</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Gdy Zdrowie &lt; tej wartości → możliwy ubytek populacji (co N tur jedna jednostka populacji umiera). [PT — do strojenia]</t>
+          <t>Modyfikator_Zdrowia = max(0, 1 + Zdrowie × wartość). Np. Zdrowie +4 → ×1,20; Zdrowie −3 → stagnacja. [PT]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-5</v>
+        <v>0.05</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=-6 … hard=-4</t>
+          <t>easy=0.06 … hard=0.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pkt Zdrowia</t>
+          <t>per pkt Zdrowia</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -11713,33 +12679,109 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>zdrowie_prog_stagnacja</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Gdy Zdrowie ≤ tego progu → wzrost populacji zatrzymany (stagnacja). Wzrost odblokowany dopiero gdy Zdrowie &gt; 0. [PT]</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>easy=0 … hard=0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pkt Zdrowia</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>society.ts zdrowie, wzrost pop</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>zdrowie_prog_ubytek_populacji</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Gdy Zdrowie &lt; tej wartości → możliwy ubytek populacji (co N tur jedna jednostka populacji umiera). [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>easy=-6 … hard=-4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pkt Zdrowia</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>society.ts zdrowie, wzrost pop</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>zdrowie_tempo_ubytku</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Co ile tur następuje utrata 1 punktu populacji, gdy Zdrowie &lt; progu ubytku. [PT — do strojenia]</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D19" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>easy=4 … hard=2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>tur/utrata</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>society.ts zdrowie, wzrost pop</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>
@@ -11756,7 +12798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12050,7 +13092,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Bonus Zadowolenia za małe miasto (populacja ≤ próg zagęszczenia). Mieszkańcy czują się mniej tłoczno. [PT]</t>
+          <t>LEGACY — zastąpione przez szczescie_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -12083,20 +13125,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>szczescie_bonus_stolica_easy</t>
+          <t>szczescie_bonus_osiedle_pop</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+          <t>D-START-OSIEDLE: bonus Sz pop 1→4. Dopasowany do celu PorPct T1 (75/55/35).</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4, 3, 2, 1</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=1 … hard=0</t>
+          <t>easy=[5, 4, 3, 2] … hard=[2, 2, 1, 0]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -12121,25 +13165,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>szczescie_kara_wielkosc_miasta</t>
+          <t>szczescie_bonus_stolica_easy</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia za każdy punkt populacji powyżej progu zagęszczenia (zagęszczenie → niezadowolenie). [PT]</t>
+          <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=1 … hard=0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pkt/1 ludności</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -12159,25 +13203,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>szczescie_prog_zagęszczenia</t>
+          <t>szczescie_kara_wielkosc_miasta</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Próg zagęszczenia dla szczęścia — poniżej tej liczby mieszkańców kara zagęszczenia nie jest naliczana. [PT]</t>
+          <t>Kara Zadowolenia za każdy punkt populacji powyżej progu zagęszczenia (zagęszczenie → niezadowolenie). [PT]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>-0.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=-0.5 … hard=-1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ludność</t>
+          <t>pkt/1 ludności</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -12197,25 +13241,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>szczescie_kara_wojna</t>
+          <t>szczescie_prog_zagęszczenia</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia w czasie stanu wojennego (zmęczenie wojną — dotyczy całej cywilizacji). [PT]</t>
+          <t>Próg zagęszczenia dla szczęścia — poniżej tej liczby mieszkańców kara zagęszczenia nie jest naliczana. [PT]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=-2 … hard=-4</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>pkt Zadowolenia</t>
+          <t>ludność</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -12235,20 +13279,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>szczescie_kara_obca_kultura</t>
+          <t>szczescie_kara_wojna</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia za dominującą obcą kulturę w mieście (&lt;50% własnej kultury). [PT — do strojenia]</t>
+          <t>Kara Zadowolenia w czasie stanu wojennego (zmęczenie wojną — dotyczy całej cywilizacji). [PT]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -12273,20 +13317,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>szczescie_kara_obca_religia</t>
+          <t>szczescie_kara_obca_kultura</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia gdy obca religia dominuje w mieście (po podboju). [PT]</t>
+          <t>Kara Zadowolenia za dominującą obcą kulturę w mieście (&lt;50% własnej kultury). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -12311,25 +13355,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>szczescie_kara_wysokie_podatki</t>
+          <t>szczescie_kara_obca_religia</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia za każdy poziom powyżej bazowej stawki podatkowej (wyższe podatki → gniew). [PT — do strojenia]</t>
+          <t>Kara Zadowolenia gdy obca religia dominuje w mieście (po podboju). [PT]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=0 … hard=-2</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>pkt/poziom</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -12349,25 +13393,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_30</t>
+          <t>szczescie_kara_wysokie_podatki</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Bonus Szczęścia gdy udział Luksus/Wealth ≥ 30% (niskie podatki). [B2-narzedzia-stabilizacji]</t>
+          <t>Kara Zadowolenia za każdy poziom powyżej bazowej stawki podatkowej (wyższe podatki → gniew). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=0 … hard=-2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>pkt/poziom</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -12387,20 +13431,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_40</t>
+          <t>szczescie_bonus_luksus_30</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy Luksus ≥ 40%.</t>
+          <t>Bonus Szczęścia gdy udział Zamożność (suwak handlu) ≥ 30% — niskie podatki. [B2-narzedzia-stabilizacji]</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -12425,20 +13469,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_50</t>
+          <t>szczescie_bonus_luksus_40</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy Luksus ≥ 50%.</t>
+          <t>Bonus Sz gdy udział Zamożność (suwak handlu) ≥ 40%.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -12463,20 +13507,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_60</t>
+          <t>szczescie_bonus_luksus_50</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy Luksus ≥ 60%.</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 50%.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -12501,20 +13545,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_70</t>
+          <t>szczescie_bonus_luksus_60</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy Luksus ≥ 70% (max).</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 60%.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=6 … hard=4</t>
+          <t>easy=5 … hard=3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -12539,25 +13583,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>szczescie_prog_bunt</t>
+          <t>szczescie_bonus_luksus_70</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 70% (max suwaka).</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>niezadowoleni</t>
+          <t>pkt Sz</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -12577,25 +13621,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>szczescie_prog_strajk_produkcja</t>
+          <t>szczescie_prog_bunt</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
+          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-1</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>niezadowoleni</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -12615,25 +13659,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>szczescie_prog_bonus_wzrost</t>
+          <t>szczescie_prog_strajk_produkcja</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
+          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=2 … hard=4</t>
+          <t>easy=-1 … hard=-1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>zadowoleni</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -12653,25 +13697,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>szczescie_bonus_wzrost_wartosc</t>
+          <t>szczescie_prog_bonus_wzrost</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>easy=0.12 … hard=0.08</t>
+          <t>easy=2 … hard=4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>zadowoleni</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -12691,25 +13735,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>szczescie_prog_bonus_produkcja</t>
+          <t>szczescie_bonus_wzrost_wartosc</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
+          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>easy=4 … hard=6</t>
+          <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>zadowoleni</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -12729,33 +13773,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>szczescie_prog_bonus_produkcja</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=6</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>zadowoleni</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>society.ts szczęście, Porządek</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>szczescie_bonus_produkcja_wartosc</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Mnożnik produkcji (Pracy) przy bardzo wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% Pracy. [PT — do strojenia]</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>0.1</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>society.ts szczęście, Porządek</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>

--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Próg wzrostu populacji: Próg(N) = 20 + N × wartość. Większy = wolniejszy wzrost. Maciej 2026-07-09: 2× żywność do wzrostu (baza 10→20 w kodzie + wsp. podwojone easy/normal/hard). [PT]</t>
+          <t>Próg wzrostu populacji: Próg(N) = 20 + N × wartość (baza 20 w kodzie, economy.ts/turn-economy.ts). Większy = wolniejszy wzrost. Wartości finalne. [PT]</t>
         </is>
       </c>
       <c r="D2" t="n">

--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -4021,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Obróbka żelaza</t>
+          <t>Hutnictwo żelaza</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Wojskowosc</t>
+          <t>Wojskowość</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Obróbka żelaza</t>
+          <t>Hutnictwo żelaza</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Hutnictwo żelaza</t>
+          <t>Obróbka żelaza</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Kodeks prawa</t>
+          <t>Prawo</t>
         </is>
       </c>
     </row>
@@ -6496,62 +6496,62 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Kodeks prawa</t>
+          <t>Prawo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>laznia_publiczna</t>
+          <t>trybunal</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Łaźnia publiczna</t>
+          <t>Trybunał</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6570,23 +6570,23 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Medycyna</t>
+          <t>Kodeks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lazaret</t>
+          <t>laznia_publiczna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lazaret</t>
+          <t>Łaźnia publiczna</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D35" t="n">
         <v>12</v>
@@ -6601,34 +6601,34 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -6640,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -6651,72 +6651,146 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>lazaret</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lazaret</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medycyna</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>akademia_wojskowa</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Akademia wojskowa</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>80</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>18</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>5</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>20</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
         <v>6</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Sztuka wojenna</t>
         </is>
@@ -7084,7 +7158,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>model dostępu v0.1 = boolean (złoże w zasięgu + ulepszenie); odblokowuje tech Obróbka żelaza; prereq Kuźni żelaza</t>
+          <t>model dostępu v0.1 = boolean (złoże w zasięgu + ulepszenie); odblokowuje tech Hutnictwo żelaza; prereq Kuźni żelaza</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7180,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>odblokowuje tech Hutnictwo żelaza; prereq Wielkiej Kuźni; model dostępu v0.1 = boolean</t>
+          <t>odblokowuje tech Obróbka żelaza; prereq Wielkiej Kuźni; model dostępu v0.1 = boolean</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7388,7 +7462,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7492,11 +7566,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Garncarstwo + Rolnictwo + Oswojenie zwierząt</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -7520,11 +7594,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Rolnictwo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7596,7 +7670,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7605,12 +7679,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Garncarstwo + Murarstwo + Obróbka drewna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Odlewnia brązu; Kuznia; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Falanga, Hastati, Kusznik, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Gaesatae, Soldurii, Wojownik germański, Berserker germański, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
+          <t>Odlewnia brązu; Kuznia; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -7639,16 +7713,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Deski</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Tartak</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7682,7 +7751,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7696,7 +7765,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Garncarstwo + Wymiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -7720,7 +7789,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -7734,7 +7803,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Garncarstwo + Mistycyzm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -7763,7 +7832,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7777,7 +7846,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jednostki: Konnica, Jeździec chiński, Rydwan konny, Rydwan egipski, Rydwan sumeryjski, Rydwan mykeński, Rydwan Shang, Rydwan celtycki</t>
+          <t>Jednostki: Konnica, Jeździec chiński, Rydwan konny, Rydwan egipski, Rydwan sumeryjski, Rydwan mykeński, Rydwan Shang</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -7787,7 +7856,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Wojskowosc</t>
+          <t>Wojskowość</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7796,7 +7865,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7829,11 +7898,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Pismo + Wymiana</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -7862,11 +7931,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Pismo + Żegluga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7881,7 +7950,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Prawo (Kodeks)</t>
+          <t>Kodeks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7890,11 +7959,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Pismo + Religia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Trybunał</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -7913,7 +7987,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7951,7 +8025,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -7980,88 +8054,88 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Obróbka żelaza</t>
+          <t>Astronomia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Żelazo</t>
+          <t>Brąz</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Dostęp do żelazo</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Odlewnia brązu</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brązownictwo</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>żelazo</t>
+          <t>Matematyka + Religia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kuźnia żelaza</t>
+          <t>Biblioteka: poziom Obserwatorium+ (poz. 6)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>kończy Epokę 2 / otwiera Epokę 3; jednostki żelazne (Gaesatae, Soldurii, Wojownik germański itp.) — do zdefiniowania przez UNITS; Kuźnia żelaza = NOWY budynek dla EKONOMIA</t>
+          <t>3a: Astronomia = bramka rozwoju Biblioteki do poziomu 6 (Obserwatorium) i wyzej; nie osobny budynek. prereq Matematyka+Mistycyzm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Inżynieria</t>
+          <t>Hutnictwo żelaza</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Żelazo</t>
+          <t>Brąz</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>6</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Dostęp do żelazo</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Piec hutniczy</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Budownictwo</t>
+          <t>Brązownictwo</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>żelazo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fort</t>
+          <t>Kuźnia żelaza; Jednostki: Hastati, Falanga, Drużynnik, Garnizon Harappy, Gwardia hetycka, Piechota neobabilońska, Tyrski miecznik, Gwardia Tyreńska, Thorakites, iButho z iklwa, Wojownik z żelaznym khopesh, Mur tarcz (Sargonid), Miecznik galijski, Rydwan celtycki, Konnica lancowa asyryjska, Konnica łucznicza asyryjska, Jeździec z oszczepami</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fort = NOWY budynek (obrona terenu, zasięg 10, +100% obrona przy obozowaniu — zob. civ-bonusy-obronne-mapa.md); Akwedukt ulepszony = rozszerzenie istniejącego Akweduktu</t>
+          <t>kończy Epokę 2 / otwiera Epokę 3; jednostki żelazne (Gaesatae, Soldurii, Wojownik germański itp.) — do zdefiniowania przez UNITS; Kuźnia żelaza = NOWY budynek dla EKONOMIA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oblężnictwo</t>
+          <t>Inżynieria</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8070,36 +8144,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Koszary</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Matematyka + Wojskowosc</t>
+          <t>Budownictwo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Warsztat oblężniczy; Jednostki: Katapulta</t>
+          <t>Fort</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>jednostki: Katapulta, Taran, Wieża oblężnicza (część już w UNITS — weryfikacja przez UNITS); Warsztat oblężniczy = NOWY budynek dla EKONOMIA; Katapulta wymaga tego tech (aktualizacja Tech w units.json przez UNITS)</t>
+          <t>Fort = NOWY budynek (obrona terenu, zasięg 10, +100% obrona przy obozowaniu — zob. civ-bonusy-obronne-mapa.md); Akwedukt ulepszony = rozszerzenie istniejącego Akweduktu</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Filozofia</t>
+          <t>Oblężnictwo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8112,32 +8181,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Biblioteka</t>
+          <t>Koszary</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pismo + Religia</t>
+          <t>Matematyka + Wojskowość</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Akademia; Teatr</t>
+          <t>Warsztat oblężniczy; Jednostki: Katapulta</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Akademia = NOWY budynek (nauka++); Teatr = NOWY budynek (kultura++, zadowolenie++); oba dla EKONOMIA</t>
+          <t>jednostki: Katapulta, Taran, Wieża oblężnicza (część już w UNITS — weryfikacja przez UNITS); Warsztat oblężniczy = NOWY budynek dla EKONOMIA; Katapulta wymaga tego tech (aktualizacja Tech w units.json przez UNITS)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kodeks prawa</t>
+          <t>Filozofia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8148,29 +8217,34 @@
       <c r="C28" t="n">
         <v>7</v>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Biblioteka</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prawo (Kodeks) + Pismo</t>
+          <t>Pismo + Religia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sąd; Pretorium</t>
+          <t>Akademia; Teatr</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sąd = NOWY budynek (administracja, zadowolenie+, korupcja-); Pretorium = NOWY budynek (administracja, bonus do utrzymania porządku); oba dla EKONOMIA</t>
+          <t>Akademia = NOWY budynek (nauka++); Teatr = NOWY budynek (kultura++, zadowolenie++); oba dla EKONOMIA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Drogi brukowane</t>
+          <t>Prawo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8179,31 +8253,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inżynieria + Budownictwo</t>
+          <t>Kodeks + Filozofia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sąd; Pretorium</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>T-TECH-9: ulepszenie Droga brukowana (+2 ruch, upgrade z Drogi)</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Droga brukowana</t>
+          <t>Sąd = NOWY budynek (administracja, zadowolenie+, korupcja-); Pretorium = NOWY budynek (administracja, bonus do utrzymania porządku); oba dla EKONOMIA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Medycyna</t>
+          <t>Drogi brukowane</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8212,36 +8286,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Studnia</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Filozofia + Gospodarka wodna</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Łaźnia publiczna; Lazaret</t>
+          <t>Inżynieria + Budownictwo</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Łaźnia publiczna = NOWY budynek (zadowolenie++, zdrowie++); Lazaret = NOWY budynek (odnawianie HP jednostek w mieście); oba dla EKONOMIA; styk z UNITS (regeneracja)</t>
+          <t>T-TECH-9: ulepszenie Droga brukowana (+2 ruch, upgrade z Drogi)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Droga brukowana</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hutnictwo żelaza</t>
+          <t>Medycyna</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8252,73 +8321,111 @@
       <c r="C31" t="n">
         <v>8</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>żelazo</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kuźnia żelaza</t>
+          <t>Studnia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Obróbka żelaza + Inżynieria</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>stal (prereq)</t>
+          <t>Filozofia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia</t>
+          <t>Łaźnia publiczna; Lazaret</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia = NOWY budynek (produkcja++, mnoznik jednostek++); stal = NOWY surowiec dla DANE (prereq dalszych epok); EKONOMIA dodaje surowiec; UNITS aktualizuje jednostki żelazne wyższego poziomu</t>
+          <t>Łaźnia publiczna = NOWY budynek (zadowolenie++, zdrowie++); Lazaret = NOWY budynek (odnawianie HP jednostek w mieście); oba dla EKONOMIA; styk z UNITS (regeneracja)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Obróbka żelaza</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Żelazo</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>żelazo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kuźnia żelaza</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Hutnictwo żelaza + Drogi brukowane</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>stal (prereq)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Wielka Kuźnia; Jednostki: Gaesatae, Soldurii, Wojownik germański, Berserker germański</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>185</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Wielka Kuźnia = NOWY budynek (produkcja++, mnoznik jednostek++); stal = NOWY surowiec dla DANE (prereq dalszych epok); EKONOMIA dodaje surowiec; UNITS aktualizuje jednostki żelazne wyższego poziomu</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Sztuka wojenna</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Żelazo</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>Koszary</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Oblężnictwo + Obróbka żelaza</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Akademia wojskowa</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>200</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>kończy Epokę 3 (cap v0.1); Akademia wojskowa = NOWY budynek (mnoznik sily i exp jednostek ++, prereq elitarnych jednostek żelaznych); UNITS definiuje jednostki top-tier Żelaza; EKONOMIA dodaje budynek</t>
         </is>

--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Miasto" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ekonomia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wealth" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Globalne" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budynki-eco" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teren-bonus" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zdrowie" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Szczescie" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kultura" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Religia" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porzadek" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potega-P-A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potega-opcje" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manpower-epoki" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budynki" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surowce" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technologie" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Miasto" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ekonomia" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wealth" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Globalne" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Budynki-eco" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Teren-bonus" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Zdrowie" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Szczescie" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Kultura" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Religia" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Porzadek" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Potega-P-A" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Potega-opcje" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Manpower-epoki" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Budynki" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Surowce" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Technologie" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_Eksporty" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,1468 +619,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Parametr</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Opis</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Wartość</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Zakres</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Jednostka</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Wpływ</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Plik</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>kultura_palac</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Produkcja kultury z Pałacu (stolica cywilizacji). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>easy=8 … hard=5</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>kultura_swiatynia</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Produkcja kultury ze Świątyni. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>kultura_biblioteka</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Produkcja kultury z Biblioteki (zbiorowe dziedzictwo wiedzy). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>kultura_amfiteatr</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Produkcja kultury z Amfiteatru (widowiska, sztuka, teatr). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>kultura_cud_bonus</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Bonus kultury z Cudu Świata (wartość per cud; cuda mają wyższy bonus niż standardowe budynki). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>easy=6 … hard=4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>kultura_specjalista_artysta</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Produkcja kultury Specjalisty Artysty przypisanego do miasta (+2 Kultury/turę per artysta). [PT]</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Kultura/turę</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>kultura_prog_zasieg_1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Próg kultury skumulowanej do 1. ekspansji granic (zasięg +1 pole wokół miasta). [PT]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>easy=75 … hard=125</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>pkt Kultury [PT]</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>kultura_prog_zasieg_2</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Próg kultury do 2. ekspansji granic. [PT]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>250</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>easy=188 … hard=312</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pkt Kultury [PT]</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>kultura_prog_zasieg_3</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Próg kultury do 3. ekspansji granic. [PT]</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>500</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>easy=375 … hard=625</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pkt Kultury [PT]</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>kultura_zadowolenie_100pct</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Bonus Zadowolenia gdy 100% kultury w mieście to nasza kultura (pełna jedność kulturowa). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>kultura_zadowolenie_75pct</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Bonus Zadowolenia gdy ≥75% kultury naszej (wysoka jedność kulturowa). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>kultura_zadowolenie_50pct</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Zadowolenie neutralne gdy 50% kultury naszej (mieszane miasto). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>easy=0 … hard=0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>kultura_kara_zadowolenie_lt50</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Kara Zadowolenia gdy &lt;50% kultury naszej (obca kultura dominuje → napięcia społeczne). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>easy=-0.75 … hard=-1.25</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>kultura_kara_zadowolenie_lt25</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Kara Zadowolenia gdy &lt;25% kultury naszej (wyraźna dominacja obcej kultury → ryzyko buntu). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>easy=-1 … hard=-3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_baza_tura</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Bazowa prędkość konwersji kultury podbitego terenu/miasta (% kultury własnej dodawanej na turę bez budynków). [PT]</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_swiatynia</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Dodatkowa prędkość konwersji kulturowej ze Świątyni w mieście (+% własnej kultury/turę per budynek). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>easy=1.88 … hard=1.12</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_amfiteatr</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Dodatkowa prędkość konwersji kulturowej z Amfiteatru (widowiska = soft power). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_biblioteka</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Dodatkowa prędkość konwersji kulturowej z Biblioteki. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>easy=0.62 … hard=0.38</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_cel_100pct</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Cel konwersji = 100% naszej kultury. Dopóki poniżej 100%: niezadowolenie/ryzyko buntu (malejące w miarę konwersji). [PT]</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>easy=100 … hard=100</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>kultura_konwersja_cap_tura</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Maksymalna łączna prędkość konwersji na turę (cap, niezależnie od liczby budynków kulturalnych). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>easy=6 … hard=4</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, granice</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Parametr</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Opis</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Wartość</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Zakres</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Jednostka</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Wpływ</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Plik</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>religia_prog_dominacji</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Próg % wyznawców w mieście, przy którym religia jest uznana za dominującą. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>easy=38 … hard=62</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>religia_szybkosc_szerzenia_bazowa</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Bazowa liczba sąsiednich miast, do których religia może dotrzeć na turę (bez bonusów). [PT]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>miasto/turę</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>religia_swiatynia_bonus_szerzenia</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Bonus prędkości szerzenia się religii ze Świątyni (Świątynia = centrum misji). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>miasto/turę</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>religia_szerzenie_max_dystans</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Maksymalny dystans w heksach, na który religia może się szerzyć bez budynków misyjnych. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>easy=4 … hard=2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>heksów</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>religia_zadowolenie_dominujaca</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Bonus Zadowolenia gdy nasza religia dominuje w mieście (jedność wyznaniowa). [PT]</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>religia_swiatynia_zadowolenie</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Bonus Zadowolenia ze Świątyni (wyznawcy mają poczucie przynależności duchowej). [PT]</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>zadowolony mieszk.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>religia_jednosc_bonus_produkcja</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Bonus do produkcji (Pracy) gdy &gt;80% miast cywilizacji wyznaje tę samą religię (jedność wyznaniowa). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>easy=0.06 … hard=0.04</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>religia_kara_obca</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Kara Zadowolenia gdy obca religia dominuje w mieście (po podboju lub konwersji przez rywala). [PT]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>easy=-1 … hard=-3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>religia_kara_brak_religii</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Kara Zadowolenia gdy miasto nie ma żadnej dominującej religii (brak duchowości = niepokój społeczny). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>easy=-0.75 … hard=-1.25</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pkt Zadowolenia</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>religia_bonus_dyplomacja_wspolna</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Bonus dyplomatyczny za wspólną religię z graczem sąsiednim (wspólne wartości, porozumienie). [PT]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>easy=12 … hard=8</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>pkt relacji</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>religia_kara_dyplomacja_rozna</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Kara dyplomatyczna za inną religię z graczem sąsiednim (tarcia ideologiczne). [PT]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>easy=-8 … hard=-12</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pkt relacji</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>religia_bonus_dyplomacja_misja</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Dodatkowy bonus dyplomatyczny jeśli wyslano misjonarza do cywilizacji i podjął działalność. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>easy=6 … hard=4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pkt relacji</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>religia_konwersja_bazowa</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Bazowa prędkość konwersji religijnej podbitego miasta (% wyznawców nowej religii na turę). [PT]</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>religia_konwersja_swiatynia</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Przyspieszenie konwersji religijnej ze Świątyni w podbitym mieście. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>easy=3 … hard=1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>%/turę</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>religia_konwersja_cel</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Cel konwersji = 100% wyznawców naszej religii. Dopóki poniżej: kara Zadowolenia (obca religia). [PT]</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>easy=100 … hard=100</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>culture-religion, szerzenie</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2142,30 +680,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>porzadek_waga_szczescie</t>
+          <t>kultura_palac</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Waga Szczęścia w Porządku: Porządek = round(waga_szczescie × Szczęście + waga_prawo × Prawo). D18-A: easy 55/45.</t>
+          <t>Produkcja kultury z Pałacu (stolica cywilizacji). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>easy=0.55 … hard=0.45</t>
+          <t>easy=8 … hard=5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>waga</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2180,30 +718,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>porzadek_waga_prawo</t>
+          <t>kultura_swiatynia</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Waga Prawa w Porządku (D18-A: hard 45/55).</t>
+          <t>Produkcja kultury ze Świątyni. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>easy=0.45 … hard=0.55</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>waga</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2218,30 +756,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>porzadek_prog_bunt_skrajny_pct</t>
+          <t>kultura_biblioteka</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Próg wejścia w Bunt skrajny (B2-D18). Poniżej → grace B2-Q12.</t>
+          <t>Produkcja kultury z Biblioteki (zbiorowe dziedzictwo wiedzy). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>easy=6 … hard=14</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>% PorPct</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2256,30 +794,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>porzadek_grace_tur_bunt</t>
+          <t>kultura_amfiteatr</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Tury bez rebelii po wejściu w strefę krytyczną (B2-D18).</t>
+          <t>Produkcja kultury z Amfiteatru (widowiska, sztuka, teatr). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tur</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2294,30 +832,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>porzadek_prog_t1</t>
+          <t>kultura_cud_bonus</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Próg T1: gdy Porządek &lt; T1 → niepokój ('unrest') — kary do produkcji/wzrostu i ryzyko buntu. Niższy T1 = łagodniej (easy). [PT — do strojenia]</t>
+          <t>Bonus kultury z Cudu Świata (wartość per cud; cuda mają wyższy bonus niż standardowe budynki). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=1</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pkt Porządku</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2332,30 +870,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>porzadek_prog_t2</t>
+          <t>kultura_specjalista_artysta</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Próg T2: gdy Porządek ≥ T2 → bonus Porządku ('order') — premia do produkcji i handlu. Między T1 a T2 → neutralnie. Niższy T2 = łatwiej o bonus (easy). [PT — do strojenia]</t>
+          <t>Produkcja kultury Specjalisty Artysty przypisanego do miasta (+2 Kultury/turę per artysta). [PT]</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>easy=4 … hard=8</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pkt Porządku</t>
+          <t>Kultura/turę</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2370,30 +908,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>porzadek_kara_produkcja_t1</t>
+          <t>kultura_prog_zasieg_1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Kara produkcji (Pracy) w niepokoju (Porządek &lt; T1). Mnożnik = max(0, 1 + wartość). Np. −0,15 → ×0,85 produkcji. [PT]</t>
+          <t>Próg kultury skumulowanej do 1. ekspansji granic (zasięg +1 pole wokół miasta). [PT]</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.15</v>
+        <v>100</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=-0.1 … hard=-0.2</t>
+          <t>easy=75 … hard=125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Kultury [PT]</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2408,30 +946,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>porzadek_kara_pieniadz_t1</t>
+          <t>kultura_prog_zasieg_2</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kara Pieniądza w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+          <t>Próg kultury do 2. ekspansji granic. [PT]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.15</v>
+        <v>250</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=-0.1 … hard=-0.2</t>
+          <t>easy=188 … hard=312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Kultury [PT]</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2446,30 +984,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>porzadek_kara_nauka_t1</t>
+          <t>kultura_prog_zasieg_3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Kara Nauki w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+          <t>Próg kultury do 3. ekspansji granic. [PT]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=-0.08 … hard=-0.12</t>
+          <t>easy=375 … hard=625</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Kultury [PT]</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2484,30 +1022,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>porzadek_kara_kultura_t1</t>
+          <t>kultura_zadowolenie_100pct</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kara Kultury w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+          <t>Bonus Zadowolenia gdy 100% kultury w mieście to nasza kultura (pełna jedność kulturowa). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=-0.08 … hard=-0.12</t>
+          <t>easy=6 … hard=2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2522,30 +1060,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>porzadek_kara_wzrost_t1</t>
+          <t>kultura_zadowolenie_75pct</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kara tempa wzrostu populacji w niepokoju (Porządek &lt; T1). Mnożnik = max(0, 1 + wartość). [PT — do strojenia]</t>
+          <t>Bonus Zadowolenia gdy ≥75% kultury naszej (wysoka jedność kulturowa). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.25</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=-0.15 … hard=-0.35</t>
+          <t>easy=4 … hard=0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2560,30 +1098,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>porzadek_ryzyko_buntu_t1</t>
+          <t>kultura_zadowolenie_50pct</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Ryzyko migracji buntu na turę w niepokoju (B2-Q6=C: ~5% normal). Engine losuje migrację −1/+1 pop w imperium. [PT]</t>
+          <t>Zadowolenie neutralne gdy 50% kultury naszej (mieszane miasto). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=0.03 … hard=0.05</t>
+          <t>easy=0 … hard=0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>prawdopodobieństwo/turę</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2598,30 +1136,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>porzadek_bonus_produkcja_t2</t>
+          <t>kultura_kara_zadowolenie_lt50</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Bonus produkcji (Pracy) przy wysokim Porządku (≥ T2). Mnożnik = 1 + wartość. Np. 0,10 → ×1,10. [PT — do strojenia]</t>
+          <t>Kara Zadowolenia gdy &lt;50% kultury naszej (obca kultura dominuje → napięcia społeczne). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=0.12 … hard=0.08</t>
+          <t>easy=-1.5 … hard=-2.5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2636,30 +1174,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>porzadek_bonus_handel_t2</t>
+          <t>kultura_kara_zadowolenie_lt25</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Bonus handlu (Handel) przy wysokim Porządku (≥ T2). Mnożnik = 1 + wartość. [PT — do strojenia]</t>
+          <t>Kara Zadowolenia gdy &lt;25% kultury naszej (wyraźna dominacja obcej kultury → ryzyko buntu). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>-4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=0.12 … hard=0.08</t>
+          <t>easy=-2 … hard=-6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>× (frakcja)</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Porządek T1/T2</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2674,30 +1212,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>prawo_garnizon_per_jednostka</t>
+          <t>kultura_konwersja_baza_tura</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Prawo z garnizonu — +pkt per jednostka w mieście (do cap). [B2-narzedzia-stabilizacji]</t>
+          <t>Bazowa prędkość konwersji kultury podbitego terenu/miasta (% kultury własnej dodawanej na turę bez budynków). [PT]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=25 … hard=15</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2712,30 +1250,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>prawo_garnizon_cap_jednostek</t>
+          <t>kultura_konwersja_swiatynia</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Max jednostek liczonych do Prawa (5 → PrawPct≈100%).</t>
+          <t>LEGACY (B-KULT-REL split): Świątynia = budynek religijny — konwersja kultury w kodzie NIE czyta tego wiersza. Bonus przeniesiony do religia_konwersja_swiatynia.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=5 … hard=4</t>
+          <t>easy=1.88 … hard=1.12</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>jednostki</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2750,30 +1288,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>prawo_ratusz</t>
+          <t>kultura_konwersja_amfiteatr</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Ratusza (gdy wpięty w budynki).</t>
+          <t>Dodatkowa prędkość konwersji kulturowej z Amfiteatru (widowiska = soft power). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=8 … hard=4</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2788,30 +1326,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>prawo_pretorium</t>
+          <t>kultura_konwersja_biblioteka</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Pretorium.</t>
+          <t>Dodatkowa prędkość konwersji kulturowej z Biblioteki. [KULT-BUD-01: 2%/t normal]</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=6 … hard=3</t>
+          <t>easy=2.5 … hard=1.5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2826,30 +1364,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>prawo_sad</t>
+          <t>kultura_konwersja_palac</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Sądu.</t>
+          <t>Dodatkowa prędkość konwersji kulturowej z Pałacu. [KULT-BUD-01: 2%/t normal]</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=6 … hard=3</t>
+          <t>easy=2.5 … hard=1.5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2864,30 +1402,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>prawo_palac</t>
+          <t>kultura_konwersja_stela</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Pałac — główne źródło Prawa (≈1,75× jednostka garnizonu; PT 2026-07).</t>
+          <t>Dodatkowa prędkość konwersji kulturowej ze Steli / Pomnika. [KULT-BUD-01: 0,5%/t normal]</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>0.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=45 … hard=28</t>
+          <t>easy=0.62 … hard=0.38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2902,30 +1440,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prawo_kara_brak_garnizonu</t>
+          <t>kultura_konwersja_sad</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
+          <t>Dodatkowa prędkość konwersji kulturowej z Sądu. [KULT-BUD-01: 2%/t normal]</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=2.5 … hard=1.5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2940,30 +1478,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada</t>
+          <t>kultura_konwersja_laznia</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LEGACY — zastąpione przez prawo_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+          <t>Dodatkowa prędkość konwersji kulturowej z Łaźni publicznej. [KULT-BUD-01: 1%/t normal]</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=1.25 … hard=0.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2978,32 +1516,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prawo_bonus_osiedle_pop</t>
+          <t>kultura_konwersja_cel_100pct</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>D-START-OSIEDLE: bonus Prawa pop 1→4. Cel PorPct T1 pop=1: easy ~75%, normal ~55%, hard ~35% (kult+rel).</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>28, 20, 14, 8</t>
-        </is>
+          <t>Cel konwersji = 100% naszej kultury. Dopóki poniżej 100%: niezadowolenie/ryzyko buntu (malejące w miarę konwersji). [PT]</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>easy=[32, 24, 16, 10] … hard=[22, 16, 10, 6]</t>
+          <t>easy=100 … hard=100</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3018,30 +1554,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada_prog</t>
+          <t>kultura_konwersja_cap_tura</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+          <t>Maksymalna łączna prędkość konwersji na turę (cap, niezależnie od liczby budynków kulturalnych). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>easy=4 … hard=4</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3056,30 +1592,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prawo_bonus_stolica_easy</t>
+          <t>kultura_presja_proc_tura</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
+          <t>KULT-PRESJA-03 (2026-07-23): gdy suma kultury imperium źródła &gt; obrońcy i miasto w zasięgu okolicy — przyrost udziału kultury źródła na mieście celu co turę. Symetrycznie. [WDROŻENIE: czeka działaj — tylko JSON na razie]</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>easy=1 … hard=0</t>
+          <t>easy=7 … hard=3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pkt Prawa</t>
+          <t>%/turę</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Prawo, garnizon</t>
+          <t>culture-religion, granice</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3093,13 +1629,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3160,35 +1696,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>jednostka_wojskowa</t>
+          <t>religia_prog_dominacji</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Suma M_pole armii imperium × pkt (unit-power.ts). Oblężnicze = 0 w armii polowej.</t>
+          <t>Próg % wyznawców w mieście, przy którym religia jest uznana za dominującą. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=38 … hard=62</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3198,35 +1734,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>wygrana_bitwa</t>
+          <t>religia_szybkosc_szerzenia_bazowa</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Legacy flat: liczba wygranych × pkt. P-C2-DEF A: model enemy_m — składnik = suma M_pole wroga (coeff 1).</t>
+          <t>Bazowa liczba sąsiednich miast, do których religia może dotrzeć na turę (bez bonusów). [PT]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>miasto/turę</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3236,35 +1772,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ludek</t>
+          <t>religia_swiatynia_bonus_szerzenia</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Suma slotów populacji (ludki) we wszystkich miastach — NIE ludność absolutna. @10 miast typowo ~100 ludków.</t>
+          <t>Bonus prędkości szerzenia się religii ze Świątyni (Świątynia = centrum misji). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>miasto/turę</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3274,35 +1810,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rekrut_ekw_jednostki</t>
+          <t>religia_szerzenie_max_dystans</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Ekwiwalent jednostek z puli Manpower: floor(rekruci / koszt_werbu[epoka]). Pełna pula ≈ ludki×10 szt. @ ep.1.</t>
+          <t>Maksymalny dystans w heksach, na który religia może się szerzyć bez budynków misyjnych. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>heksów</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3312,35 +1848,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>miasto</t>
+          <t>religia_zadowolenie_dominujaca</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Każde miasto imperium.</t>
+          <t>Bonus Zadowolenia gdy nasza religia dominuje w mieście (jedność wyznaniowa). [PT]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=6 … hard=2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3350,35 +1886,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>heks_terytorium</t>
+          <t>religia_swiatynia_zadowolenie</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Heks w zasięgu terytorium miast (isInTerritory).</t>
+          <t>Bonus Zadowolenia ze Świątyni (wyznawcy mają poczucie przynależności duchowej). [PT]</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>zadowolony mieszk.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3388,35 +1924,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>budynki</t>
+          <t>religia_jednosc_bonus_produkcja</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Każdy wybudowany budynek we wszystkich miastach.</t>
+          <t>Bonus do produkcji (Pracy) gdy &gt;80% miast cywilizacji wyznaje tę samą religię (jedność wyznaniowa). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=0.06 … hard=0.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3426,35 +1962,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tech_zbadane</t>
+          <t>religia_kara_obca</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Liczba zbadanych technologii imperium.</t>
+          <t>Kara Zadowolenia gdy obca religia dominuje w mieście (po podboju lub konwersji przez rywala). [PT]</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=-2 … hard=-6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3464,35 +2000,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ulepszenie_terenu</t>
+          <t>religia_kara_brak_religii</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Ulepszenia terenu w terytorium imperium (farmy, drogi, hodowla…).</t>
+          <t>Kara Zadowolenia gdy miasto nie ma żadnej dominującej religii (brak duchowości = niepokój społeczny). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>&gt;= 0</t>
+          <t>easy=-1.5 … hard=-2.5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pkt</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+          <t>culture-religion, szerzenie</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>power-params.json → skladniki.*.pkt</t>
+          <t>society-params.json</t>
         </is>
       </c>
     </row>
@@ -3502,33 +2038,1877 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>religia_bonus_dyplomacja_wspolna</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Bonus dyplomatyczny za wspólną religię z graczem sąsiednim (wspólne wartości, porozumienie). [PT]</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>easy=12 … hard=8</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pkt relacji</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>religia_kara_dyplomacja_rozna</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kara dyplomatyczna za inną religię z graczem sąsiednim (tarcia ideologiczne). [PT]</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>easy=-8 … hard=-12</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pkt relacji</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>religia_bonus_dyplomacja_misja</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Dodatkowy bonus dyplomatyczny jeśli wyslano misjonarza do cywilizacji i podjął działalność. [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pkt relacji</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>religia_konwersja_bazowa</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bazowa prędkość konwersji religijnej podbitego miasta (% wyznawców nowej religii na turę). [PT]</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>easy=3 … hard=1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>%/turę</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>religia_konwersja_swiatynia</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bonus konwersji religijnej ze Świątyni — DODAWANY do religia_konwersja_bazowa (normal: +4%/t → łącznie 6%/t). Budynek religijny — bez bonusu konwersji kultury. [KULT-BUD-02]</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>%/turę</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>religia_konwersja_kregi</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Bonus konwersji religijnej z Kamiennych kręgów — DODAWANY do religia_konwersja_bazowa (normal: +2%/t → łącznie 4%/t). [KULT-BUD-02]</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>easy=3 … hard=1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>%/turę</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>religia_konwersja_cel</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Cel konwersji = 100% wyznawców naszej religii. Dopóki poniżej: kara Zadowolenia (obca religia). [PT]</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>easy=100 … hard=100</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>religia_presja_proc_tura</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>KULT-PRESJA-04 (2026-07-23): mirror kultura_presja_proc_tura — gdy suma religii imperium źródła &gt; obrońcy i miasto w zasięgu okolicy — przyrost udziału religii źródła na mieście celu co turę. Symetrycznie (06). [WDROŻENIE: czeka działaj — tylko JSON na razie]</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>easy=7 … hard=3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>%/turę</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>culture-religion, szerzenie</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Zakres</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wpływ</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Plik</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>porzadek_waga_szczescie</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Waga Szczęścia w Porządku: Porządek = round(waga_szczescie × Szczęście + waga_prawo × Prawo). D18-A: easy 55/45.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>easy=0.55 … hard=0.45</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>waga</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>porzadek_waga_prawo</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Waga Prawa w Porządku (D18-A: hard 45/55).</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>easy=0.45 … hard=0.55</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>waga</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>porzadek_prog_bunt_skrajny_pct</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Próg wejścia w Bunt skrajny (B2-D18). Poniżej → grace B2-Q12.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=14</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>% PorPct</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>porzadek_grace_tur_bunt</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tury bez rebelii po wejściu w strefę krytyczną (B2-D18).</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tur</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>porzadek_prog_t1</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Próg T1: gdy Porządek &lt; T1 → niepokój ('unrest') — kary do produkcji/wzrostu i ryzyko buntu. Niższy T1 = łagodniej (easy). [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>easy=-1 … hard=1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pkt Porządku</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>porzadek_prog_t2</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Próg T2: gdy Porządek ≥ T2 → bonus Porządku ('order') — premia do produkcji i handlu. Między T1 a T2 → neutralnie. Niższy T2 = łatwiej o bonus (easy). [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pkt Porządku</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>porzadek_kara_produkcja_t1</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Kara produkcji (Pracy) w niepokoju (Porządek &lt; T1). Mnożnik = max(0, 1 + wartość). Np. −0,15 → ×0,85 produkcji. [PT]</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>easy=-0.1 … hard=-0.2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>porzadek_kara_pieniadz_t1</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kara Pieniądza w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>easy=-0.1 … hard=-0.2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>porzadek_kara_nauka_t1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Kara Nauki w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>easy=-0.08 … hard=-0.12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>porzadek_kara_kultura_t1</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Kara Kultury w niepokoju (B2-Q6). Mnożnik = max(0, 1 + wartość). [PT]</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>easy=-0.08 … hard=-0.12</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>porzadek_kara_wzrost_t1</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kara tempa wzrostu populacji w niepokoju (Porządek &lt; T1). Mnożnik = max(0, 1 + wartość). [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>easy=-0.15 … hard=-0.35</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>porzadek_ryzyko_buntu_t1</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Ryzyko migracji buntu na turę w niepokoju (B2-Q6=C: ~5% normal). Engine losuje migrację −1/+1 pop w imperium. [PT]</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>easy=0.03 … hard=0.05</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>prawdopodobieństwo/turę</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>porzadek_bonus_produkcja_t2</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Bonus produkcji (Pracy) przy wysokim Porządku (≥ T2). Mnożnik = 1 + wartość. Np. 0,10 → ×1,10. [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>easy=0.12 … hard=0.08</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>porzadek_bonus_handel_t2</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Bonus handlu (Handel) przy wysokim Porządku (≥ T2). Mnożnik = 1 + wartość. [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>easy=0.12 … hard=0.08</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>× (frakcja)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Porządek T1/T2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prawo_garnizon_per_jednostka</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Prawo z garnizonu — +pkt per jednostka w mieście (do cap). [B2-narzedzia-stabilizacji]</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>easy=25 … hard=15</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prawo_garnizon_cap_jednostek</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Max jednostek liczonych do Prawa (5 → PrawPct≈100%).</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>easy=5 … hard=4</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jednostki</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prawo_ratusz</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Bonus Prawa z Ratusza (gdy wpięty w budynki).</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>easy=8 … hard=4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prawo_pretorium</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Bonus Prawa z Pretorium.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prawo_sad</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Bonus Prawa z Sądu.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prawo_palac</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Pałac — główne źródło Prawa (≈1,75× jednostka garnizonu; PT 2026-07).</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>easy=45 … hard=28</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prawo_kara_brak_garnizonu</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>easy=-1 … hard=-3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prawo_kara_podboj_bez_garnizonu</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Kara Prawa gdy po podboju obca kultura+religia i brak jednostek w mieście. [B-KULT-REL]</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>easy=-2 … hard=-4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osada</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>LEGACY — zastąpione przez prawo_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osiedle_pop</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>D-START-OSIEDLE: bonus Prawa pop 1→4. Cel PorPct T1 pop=1: easy ~75%, normal ~55%, hard ~35% (kult+rel).</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>28, 20, 14, 8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>easy=[32, 24, 16, 10] … hard=[22, 16, 10, 6]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osada_prog</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=4</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prawo_bonus_stolica_easy</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Zakres</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wpływ</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Plik</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>jednostka_wojskowa</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Suma M_pole armii imperium × pkt (unit-power.ts). Oblężnicze = 0 w armii polowej.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wygrana_bitwa</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Legacy flat: liczba wygranych × pkt. P-C2-DEF A: model enemy_m — składnik = suma M_pole wroga (coeff 1).</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ludek</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Suma slotów populacji (ludki) we wszystkich miastach — NIE ludność absolutna. @10 miast typowo ~100 ludków.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rekrut_ekw_jednostki</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ekwiwalent jednostek z puli Manpower: floor(rekruci / koszt_werbu[epoka]). Pełna pula ≈ ludki×10 szt. @ ep.1.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>miasto</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Każde miasto imperium.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>heks_terytorium</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Heks w zasięgu terytorium miast (isInTerritory).</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>budynki</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Każdy wybudowany budynek we wszystkich miastach.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tech_zbadane</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Liczba zbadanych technologii imperium.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ulepszenie_terenu</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Ulepszenia terenu w terytorium imperium (farmy, drogi, hodowla…).</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>kultura_imperium</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KULT-04 A — suma kulturaSkumulowana wszystkich miast imperium × pkt.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>religia_jednosc</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>KULT-04 A — każde miasto z dominującą wiarą państwa × pkt.</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>&gt;= 0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pkt</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>power-objective.ts → computeObjectivePower (globalny kanon)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>power-params.json → skladniki.*.pkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>_kalibracja_power_oczekiwany</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>INFO: scenariusz testowy Macieja (nie eksportowane do silnika)</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>3020</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>pkt</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>power-objective-test.cjs</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>power-params.json → skladniki.*.pkt</t>
         </is>
@@ -3881,7 +4261,7 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -3895,7 +4275,7 @@
         <v>2000</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -3909,7 +4289,7 @@
         <v>4000</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="5">
@@ -3923,7 +4303,7 @@
         <v>8000</v>
       </c>
       <c r="D5" t="n">
-        <v>800</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="6">
@@ -3937,7 +4317,7 @@
         <v>16000</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="7">
@@ -3951,7 +4331,7 @@
         <v>32000</v>
       </c>
       <c r="D7" t="n">
-        <v>3200</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="8">
@@ -3965,7 +4345,7 @@
         <v>64000</v>
       </c>
       <c r="D8" t="n">
-        <v>6400</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="9">
@@ -3979,7 +4359,7 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>12000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="10">
@@ -3993,7 +4373,7 @@
         <v>240000</v>
       </c>
       <c r="D10" t="n">
-        <v>24000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="11">
@@ -4007,7 +4387,7 @@
         <v>480000</v>
       </c>
       <c r="D11" t="n">
-        <v>48000</v>
+        <v>480000</v>
       </c>
     </row>
   </sheetData>
@@ -4213,19 +4593,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mielerz</t>
+          <t>kamieniarski</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mielerz</t>
+          <t>Warsztat kamieniarski</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -4280,36 +4660,36 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Obróbka drewna</t>
+          <t>Murarstwo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kamieniarski</t>
+          <t>kuznia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Warsztat kamieniarski</t>
+          <t>Kuznia</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -4326,51 +4706,51 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Murarstwo</t>
+          <t>Brązownictwo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>kuznia</t>
+          <t>odlewnia_brazu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kuznia</t>
+          <t>Piec hutniczy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -4379,10 +4759,10 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4400,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
@@ -4424,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -4435,28 +4815,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>odlewnia_brazu</t>
+          <t>odlewnia_zelaza</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Piec hutniczy</t>
+          <t>Odlewnia żelaza</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -4477,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -4502,36 +4882,36 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Brązownictwo</t>
+          <t>Hutnictwo żelaza</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>odlewnia_zelaza</t>
+          <t>targowisko</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Odlewnia żelaza</t>
+          <t>Targowisko (Rynek)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -4551,10 +4931,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -4572,64 +4952,64 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Hutnictwo żelaza</t>
+          <t>Wymiana</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>targowisko</t>
+          <t>port</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Targowisko (Rynek)</t>
+          <t>Port handlowy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -4646,40 +5026,40 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Wymiana</t>
+          <t>Żegluga</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>port_wielki</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Port handlowy</t>
+          <t>Port wielki</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -4702,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -4724,60 +5104,60 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Żegluga</t>
+          <t>Inżynieria</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>port_wielki</t>
+          <t>karawanseraj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Port wielki</t>
+          <t>Karawanseraj</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>6</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -4794,43 +5174,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Inżynieria</t>
+          <t>Handel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>karawanseraj</t>
+          <t>spichlerz</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Karawanseraj</t>
+          <t>Spichlerz</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -4844,16 +5224,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -4868,33 +5248,33 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Handel</t>
+          <t>Garncarstwo</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>spichlerz</t>
+          <t>spichlerz_ii</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spichlerz</t>
+          <t>Spichlerz II</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -4903,16 +5283,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -4946,7 +5326,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Garncarstwo</t>
+          <t>Warzelnia soli</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -5279,7 +5659,7 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -5906,7 +6286,11 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6385,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
@@ -6409,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -6607,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
@@ -6807,7 +7191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6872,7 +7256,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>budulec; wejscie Tartaku i Mielerza</t>
+          <t>budulec; wejscie Tartaku i konwerterow (Cegielnia/Garncarnia/Piec hutniczy/Odlewnia zelaza/Wielka Kuznia) 1:1 zamiast dawnego Paliwa</t>
         </is>
       </c>
     </row>
@@ -6933,41 +7317,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>złoże Ruda + Kopalnia</t>
+          <t>złoże miedzi + Kopalnia miedzi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>wejscie Huty</t>
+          <t>wejscie Odlewni brązu (klucz stock: ruda)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bydło (krowa/wół)</t>
+          <t>Ruda żelaza</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hodowla</t>
+          <t>surowy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>złoże/handel (zarodek) + Bydło</t>
+          <t>złoże żelaza + Kopalnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pierwsze pastwisko na złożu odblokowuje hodowle imperium; bonus pola +2 żywności / +3 produkcji (kanon); Rydwan; Inkowie od epoki 3</t>
+          <t>wejscie Odlewni żelaza (klucz stock: ruda_zelaza)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Owce</t>
+          <t>Koń</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6977,63 +7361,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>złoże/handel (zarodek) + Owce</t>
+          <t>złoże Konie / Stajnia (później)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>solo wzgórze; +1 żywności / +2 produkcji; pierwsze na złożu odblokowuje imperium; Inkowie od epoki 3</t>
+          <t>Konnica (Brąz) i rydwany konne; NIEDOSTĘPNY u Majów/Ameryki (konie wyginęły w Nowym Świecie ~10 000 p.n.e.)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lama</t>
+          <t>Sól</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hodowla</t>
+          <t>surowy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>złoże/handel (zarodek) + Lama</t>
+          <t>złoże Sól (wybrzeże) + Warzelnia soli</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TYLKO Inkowie; solo; +1 żywności / +3 produkcji; pierwsze na złożu lamy odblokowuje imperium; brak Rydwanu</t>
+          <t>bramka Spichlerz II; konserwacja żywności</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Koń</t>
+          <t>Cegła</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hodowla</t>
+          <t>przetworzony</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>złoże Konie / Stajnia (później)</t>
+          <t>Cegielnia (glina+drewno)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Konnica (Brąz) i rydwany konne; NIEDOSTĘPNY u Majów/Ameryki (konie wyginęły w Nowym Świecie ~10 000 p.n.e.)</t>
+          <t>budulec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deski</t>
+          <t>Ceramika</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7043,19 +7427,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tartak (z drewna)</t>
+          <t>Garncarnia (glina+drewno)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>budulec</t>
+          <t>+zadowolenie, +Zdrowie</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paliwo (węgiel drzewny)</t>
+          <t>Brąz</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7065,41 +7449,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mielerz (z drewna)</t>
+          <t>Piec hutniczy (ruda+drewno)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>wejscie Cegielni, Garncarni i Huty</t>
+          <t>budulec + jednostki brazowe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cegła</t>
+          <t>Żelazo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>przetworzony</t>
+          <t>surowy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cegielnia (glina+paliwo)</t>
+          <t>złoże Ruda żelaza + Kuźnia żelaza</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>budulec</t>
+          <t>model dostępu v0.1 = boolean (złoże w zasięgu + ulepszenie); odblokowuje tech Hutnictwo żelaza; prereq Kuźni żelaza</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ceramika</t>
+          <t>Stal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7109,76 +7493,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Garncarnia (z gliny)</t>
+          <t>Wielka Kuźnia (żelazo+drewno)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>+zadowolenie, +Zdrowie</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Brąz</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>przetworzony</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Huta (ruda+paliwo)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>budulec + jednostki brazowe</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Żelazo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>surowy</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>złoże Ruda żelaza + Kuźnia żelaza</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>model dostępu v0.1 = boolean (złoże w zasięgu + ulepszenie); odblokowuje tech Hutnictwo żelaza; prereq Kuźni żelaza</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Stal</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>przetworzony</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Wielka Kuźnia (żelazo+paliwo)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>odblokowuje tech Obróbka żelaza; prereq Wielkiej Kuźni; model dostępu v0.1 = boolean</t>
         </is>
@@ -7281,12 +7599,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>deski, paliwo, drewno</t>
+          <t>drewno</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Stolarnia, Mielerz</t>
+          <t>Stolarnia</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7471,7 +7789,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Łowiectwo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7717,7 +8035,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deski</t>
+          <t>Drewno</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8637,11 +8955,11 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Ile ludnosci kosztuje miasto ukonczenie jednostki z kolejki (rekrutacja). production.populationCostOf; odjecie + clamp do min.1 robi petla tury.</t>
+          <t>Koszt ludnosci miasta za ukonczenie jednostki z kolejki (rekrutacja). USTAWIONE 0 (Maciej 2026-07-21): rekrutacja NIE zabiera juz populacji miasta — jedynym kosztem werbu jest pula Manpower (epoka-ludnosc-manpower.json / manpower.ts). production.populationCostOf; przy 0 populacja pozostaje bez zmian.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
@@ -8671,11 +8989,11 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Co koniec tury miasto odzyskuje floor(manpowerMax × wartosc/100) Manpower (do cap). Ep1, 10 ludkow, max=10k → +1000/ture. Pusta pula ≈10 tur do pelna. manpower.tickManpowerRegen.</t>
+          <t>Co koniec tury miasto odzyskuje floor(manpowerMax × wartosc/100) Manpower (do cap). Ep1, 10 ludkow, max=10k → +200/ture. Pusta pula ≈50 tur do pelna. manpower.tickManpowerRegen.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
@@ -10623,7 +10941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10727,7 +11045,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik Mennicy aktywny po odkryciu technologii Waluta. [PT — docelowo ×1,5–×2,0]</t>
+          <t>Mnożnik Mennicy (Handel→Pieniądz) aktywny TYLKO gdy Mennica zbudowana ORAZ technologia Waluta odkryta w mieście. Wartości właściciela (Q5=A, 2026-07-20): easy ×2 / normal ×1,5 / hard ×1 (hard = bez bonusu, ale nie zeruje dochodu). Wcześniej 1.88/1.5/1.12 mimo że mennicaMnoznik był zahardkodowany na 1 w turn-economy.ts (Mennica nic nie robiła) — naprawione E1 zadanie 1.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -10735,7 +11053,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>easy=1.88 … hard=1.12</t>
+          <t>easy=2 … hard=1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -10841,20 +11159,20 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Bazowa pojemność per typ surowca (bez Magazynu Surowców). [PT]</t>
+          <t>SUROW-CIV-01 (decyzja Macieja 2026-07-24): ZMIANA SEMANTYKI — od teraz to baza pojemności CAŁEGO PAŃSTWA (civ-wide, suma po wszystkich miastach ownera) per typ surowca, przy 0 zbudowanych budynków „Magazyn” w imperium — NIE per-miasto jak dawniej. Model ADDYTYWNY razem z magazyn_bonus_surowce_na_budynek (nie mnożnikowy). Placeholder do strojenia; wartości easy/normal/hard zachowują dawną proporcję 1,2/1/0,8. Dotyczy WYŁĄCZNIE surowców (drewno/kamień/glina/ruda/ruda_zelaza/cegła/brąz/żelazo/stal) — Żywność/Spichlerz nadal używa modelu mnożnikowego per-miasto (bez zmian, patrz magazyn_baza_zywnosc).</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=12 … hard=8</t>
+          <t>easy=100 … hard=100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>szt/typ surowca</t>
+          <t>szt/typ surowca (PAŃSTWO)</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -10874,25 +11192,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>magazyn_mnoznik_spichlerz</t>
+          <t>magazyn_bonus_surowce_na_budynek</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik pojemności przy wybudowanym Spichlerzu / Magazynie Surowców. [PT]</t>
+          <t>SUROW-CIV-01 (decyzja Macieja 2026-07-24, NOWY PARAMETR): dodatkowa pojemność CAŁEGO PAŃSTWA per typ surowca za KAŻDY budynek „Magazyn” zbudowany GDZIEKOLWIEK w imperium ownera (addytywnie, nie mnożnik — 2 Magazyny = +200, nie ×2). Cap per typ = magazyn_baza_surowce + magazyn_bonus_surowce_na_budynek × liczba_magazynow. Placeholder do strojenia.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>easy=6 … hard=4</t>
+          <t>easy=100 … hard=100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>szt/typ surowca (PAŃSTWO) / Magazyn</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -10912,25 +11230,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>utrzymanie_jednostka_standard</t>
+          <t>magazyn_mnoznik_spichlerz</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Koszt utrzymania standardowej jednostki wojskowej. [PT]</t>
+          <t>Mnożnik pojemności ŻYWNOŚCI przy wybudowanym Spichlerzu (magazyn_baza_zywnosc × ten mnożnik). SUROW-CIV-01 2026-07-24: surowce (drewno/kamień/…) NIE używają już tego mnożnika — patrz magazyn_baza_surowce/magazyn_bonus_surowce_na_budynek (model addytywny, civ-wide). [PT]</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pieniądz/turę</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -10950,35 +11268,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>utrzymanie_jednostka_standard</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Koszt utrzymania standardowej jednostki wojskowej. [PT]</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pieniądz/turę</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>skarbiec_centralny_lokalizacja</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Skarbiec zawsze w stolicy; utrata stolicy zeruje go do 0.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>stolica</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>easy=stolica … hard=stolica</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>miasto</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>economy, magazyny</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -10995,7 +11351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11208,25 +11564,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>budynek_mennica_mnoznik</t>
+          <t>budynek_stolarnia_bonus_drewna_civ</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik Mennicy (Handel→Pieniądz). Docelowo ×1,5–×2,0 po upgrade. [PT]</t>
+          <t>Zadanie 2 (2026-07-23): Stolarnia +10% produkcji Drewna CALEJ CYWILIZACJI za kazda Stolarnie (civ-wide, stackuje addytywnie: ×(1+0.10×liczbaStolarni_ownera)). Wpiete w turn-economy.ts przy akumulacji City.surowce.drewno. PLACEHOLDER do strojenia.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=0.1 … hard=0.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -11246,20 +11602,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>budynek_biblioteka_bonus_nauki</t>
+          <t>budynek_kamieniarski_bonus_kamienia_civ</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Premia Biblioteki do Nauki lokalnie (+50%). [PT — do strojenia]</t>
+          <t>Zadanie 2 (2026-07-23): Warsztat kamieniarski +10% produkcji Kamienia CALEJ CYWILIZACJI za kazda sztuke (civ-wide, stackuje addytywnie: ×(1+0.10×liczbaWarsztatow_ownera)). Wpiete w turn-economy.ts przy akumulacji City.surowce.kamien. PLACEHOLDER do strojenia.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>easy=0.62 … hard=0.38</t>
+          <t>easy=0.1 … hard=0.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -11284,25 +11640,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>waluta_mnoznik</t>
+          <t>budynek_garncarnia_bonus_zywnosci_lokalnie</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Efekt 1 (Waluta tech): mnoznik na caly handelNetto miasta gdy walutaOdkryta=true (×2 na cala pule Handlu przed podzialem). Dotyczy wszystkich miast automatycznie po wynalezieniu Waluty.</t>
+          <t>Zadanie 2 (2026-07-23): Garncarnia +10% Zywnosci LOKALNIE (tylko w miescie, gdzie stoi; NIE civ-wide), stackuje addytywnie: ×(1+0.10×garncarnie_w_miescie). Wpiete w economy.ts cityYieldPerTurn (zywnoscBrutto, przed konsumpcja). PLACEHOLDER do strojenia.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=2 … hard=2</t>
+          <t>easy=0.1 … hard=0.1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -11322,25 +11678,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>targowisko_praca_na_pieniadz_mnoznik</t>
+          <t>ulepszenie_surowcowe_upkeep_praca</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Efekt 2 (Targowisko + Waluta): mnoznik konwersji puli-Pracy (doPuli) na Pieniadz. Aktywny per-miasto gdy maTargowisko=true i walutaOdkryta=true. pieniadzZPracy = floor(doPuli × mnoznik).</t>
+          <t>ZADANIE 1 (Maciej 2026-07-23, decyzja B): KAZDE zbudowane ulepszenie surowcowe (tartak/kamieniolom/glinianka/kopalnia/kopalnia_miedzi + DOSTEPOWE warzelnia_soli/stadnina) zuzywa 1 Praca/ture z globalnej puli produkcji cywilizacji (playerPracaPool / aiPracaPoolByOwner w main.ts) -- ciagly upkeep, niezaleznie od obsadzenia ludnoscia. Zwolnione: zywnosciowe (farma/irygacja/tarasy/bydlo/owce/lama/oboz_lowiecki/lodzie_rybackie) + infrastruktura (droga/droga_brukowana/fort/posterunek/wyrab). Wpiete w turn-economy.ts computePracaUpkeepByOwner. PLACEHOLDER do strojenia (koszt=1).</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=2 … hard=2</t>
+          <t>easy=1 … hard=1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>Praca/turę/ulepszenie</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -11360,25 +11716,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>budynek_tartak_przepustowosc</t>
+          <t>budynek_mennica_mnoznik</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja Drewno→Deski w Tartaku na turę. [PT]</t>
+          <t>Mnożnik Mennicy (Handel→Pieniądz). Docelowo ×1,5–×2,0 po upgrade. [PT]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>szt/turę</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -11398,25 +11754,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>budynek_mielerz_przepustowosc</t>
+          <t>budynek_biblioteka_bonus_nauki</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja Drewno→Paliwo w Mielerzni na turę. [PT]</t>
+          <t>Premia Biblioteki do Nauki lokalnie (+50%). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=0.62 … hard=0.38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>szt/turę</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -11436,12 +11792,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>budynek_cegielnia_przepustowosc</t>
+          <t>waluta_mnoznik</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Glina+Paliwo)→Cegła w Cegielni na turę. [PT]</t>
+          <t>Efekt 1 (Waluta tech): mnoznik na caly handelNetto miasta gdy walutaOdkryta=true (×2 na cala pule Handlu przed podzialem). Dotyczy wszystkich miast automatycznie po wynalezieniu Waluty.</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -11449,12 +11805,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>szt/turę</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -11474,25 +11830,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>budynek_huta_przepustowosc</t>
+          <t>targowisko_praca_na_pieniadz_mnoznik</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Ruda+Paliwo)→Brąz w Hucie na turę. [PT]</t>
+          <t>Efekt 2 (Targowisko + Waluta): mnoznik konwersji puli-Pracy (doPuli) na Pieniadz. Aktywny per-miasto gdy maTargowisko=true i walutaOdkryta=true. pieniadzZPracy = floor(doPuli × mnoznik).</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=2 … hard=2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>szt/turę</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -11512,20 +11868,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>budynek_garncarnia_przepustowosc</t>
+          <t>budynek_tartak_przepustowosc</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Glina+Paliwo)→Ceramika w Garncarni na turę. [PT]</t>
+          <t>Maks konwersja Drewno→Deski w Tartaku na turę. [PT]</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -11550,33 +11906,147 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>budynek_cegielnia_przepustowosc</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Maks konwersja (Glina+Drewno)→Cegła w Cegielni na turę. [PT] C-SUROW-CEGLA=A (Maciej 2026-07-24): normal 2→3 (odciążenie cegły wg symulacji bilansu).</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=2</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>budynek_huta_przepustowosc</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Maks konwersja (Ruda+Drewno)→Brąz w Hucie na turę. [PT]</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>easy=2 … hard=0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>budynek_garncarnia_przepustowosc</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Maks konwersja (Glina+Drewno)→Ceramika w Garncarni na turę. [PT]</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>easy=2 … hard=0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>utrzymanie_budynek</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Koszt utrzymania każdego budynku (niezróżnicowany w v0.1). [PT]</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>easy=1 … hard=2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Pieniądz/turę</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>economy.ts mnozniki</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -12677,7 +13147,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Huta, Mielerz itp.). Późne epoki. [PT]</t>
+          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Piec hutniczy, Cegielnia itp.). Późne epoki. [PT]</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -12905,7 +13375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13433,11 +13903,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=-1.5 … hard=-2.5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -13471,11 +13941,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=-2 … hard=-6</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13500,25 +13970,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>szczescie_kara_wysokie_podatki</t>
+          <t>szczescie_kara_podboj_podwojna_obca</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia za każdy poziom powyżej bazowej stawki podatkowej (wyższe podatki → gniew). [PT — do strojenia]</t>
+          <t>Dodatkowa kara Sz gdy po podboju jednocześnie obca kultura (&lt;50%) i obca dominująca religia. [B-KULT-REL]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=0 … hard=-2</t>
+          <t>easy=-1.5 … hard=-2.5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pkt/poziom</t>
+          <t>pkt Zadowolenia</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -13538,25 +14008,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_30</t>
+          <t>szczescie_kara_wysokie_podatki</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Bonus Szczęścia gdy udział Zamożność (suwak handlu) ≥ 30% — niskie podatki. [B2-narzedzia-stabilizacji]</t>
+          <t>Kara Zadowolenia za każdy poziom powyżej bazowej stawki podatkowej (wyższe podatki → gniew). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=0 … hard=-2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>pkt/poziom</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -13576,20 +14046,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_40</t>
+          <t>szczescie_bonus_luksus_30</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność (suwak handlu) ≥ 40%.</t>
+          <t>Bonus Szczęścia gdy udział Zamożność (suwak handlu) ≥ 30% — niskie podatki. [B2-narzedzia-stabilizacji]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13614,20 +14084,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_50</t>
+          <t>szczescie_bonus_luksus_40</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 50%.</t>
+          <t>Bonus Sz gdy udział Zamożność (suwak handlu) ≥ 40%.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -13652,20 +14122,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_60</t>
+          <t>szczescie_bonus_luksus_50</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 60%.</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 50%.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -13690,20 +14160,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_70</t>
+          <t>szczescie_bonus_luksus_60</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 70% (max suwaka).</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 60%.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=6 … hard=4</t>
+          <t>easy=5 … hard=3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -13728,25 +14198,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>szczescie_prog_bunt</t>
+          <t>szczescie_bonus_luksus_70</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
+          <t>Bonus Sz gdy udział Zamożność ≥ 70% (max suwaka).</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>niezadowoleni</t>
+          <t>pkt Sz</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -13766,25 +14236,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>szczescie_prog_strajk_produkcja</t>
+          <t>szczescie_prog_bunt</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
+          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-1</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>niezadowoleni</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -13804,25 +14274,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>szczescie_prog_bonus_wzrost</t>
+          <t>szczescie_prog_strajk_produkcja</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
+          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>easy=2 … hard=4</t>
+          <t>easy=-1 … hard=-1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>zadowoleni</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -13842,25 +14312,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>szczescie_bonus_wzrost_wartosc</t>
+          <t>szczescie_prog_bonus_wzrost</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>easy=0.12 … hard=0.08</t>
+          <t>easy=2 … hard=4</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>zadowoleni</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -13880,25 +14350,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>szczescie_prog_bonus_produkcja</t>
+          <t>szczescie_bonus_wzrost_wartosc</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
+          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>easy=4 … hard=6</t>
+          <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>zadowoleni</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -13918,33 +14388,71 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>szczescie_prog_bonus_produkcja</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=6</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>zadowoleni</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>society.ts szczęście, Porządek</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>szczescie_bonus_produkcja_wartosc</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Mnożnik produkcji (Pracy) przy bardzo wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% Pracy. [PT — do strojenia]</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>0.1</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>society.ts szczęście, Porządek</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>

--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -4401,7 +4401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4515,6 +4515,31 @@
           <t>techUnlock</t>
         </is>
       </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>koszt_surowce.drewno</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>koszt_surowce.kamien</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>koszt_surowce.cegla</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>koszt_surowce.braz</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>koszt_surowce.zelazo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4589,6 +4614,9 @@
           <t>Obróbka drewna</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4663,6 +4691,12 @@
           <t>Murarstwo</t>
         </is>
       </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4737,6 +4771,12 @@
           <t>Brązownictwo</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4811,6 +4851,12 @@
           <t>Brązownictwo</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4885,6 +4931,12 @@
           <t>Hutnictwo żelaza</t>
         </is>
       </c>
+      <c r="Y6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4959,6 +5011,9 @@
           <t>Wymiana</t>
         </is>
       </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5033,6 +5088,9 @@
           <t>Żegluga</t>
         </is>
       </c>
+      <c r="W8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5107,6 +5165,12 @@
           <t>Inżynieria</t>
         </is>
       </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5181,6 +5245,9 @@
           <t>Handel</t>
         </is>
       </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5255,6 +5322,12 @@
           <t>Garncarstwo</t>
         </is>
       </c>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5329,6 +5402,9 @@
           <t>Warzelnia soli</t>
         </is>
       </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5403,6 +5479,12 @@
           <t>Garncarstwo</t>
         </is>
       </c>
+      <c r="W13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5477,6 +5559,12 @@
           <t>Garncarstwo</t>
         </is>
       </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5551,6 +5639,9 @@
           <t>Mistycyzm</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5625,6 +5716,9 @@
           <t>Religia</t>
         </is>
       </c>
+      <c r="Y16" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5699,6 +5793,9 @@
           <t>Pismo</t>
         </is>
       </c>
+      <c r="Y17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5773,6 +5870,9 @@
           <t>Gospodarka wodna</t>
         </is>
       </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5847,6 +5947,9 @@
           <t>Budownictwo</t>
         </is>
       </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5921,6 +6024,12 @@
           <t>Waluta</t>
         </is>
       </c>
+      <c r="X20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5995,6 +6104,9 @@
           <t>Budownictwo</t>
         </is>
       </c>
+      <c r="Y21" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6069,6 +6181,15 @@
           <t>Wojskowość</t>
         </is>
       </c>
+      <c r="W22" t="n">
+        <v>6</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6143,6 +6264,12 @@
           <t>Handel</t>
         </is>
       </c>
+      <c r="W23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6217,6 +6344,9 @@
           <t>Murarstwo</t>
         </is>
       </c>
+      <c r="X24" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6291,6 +6421,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="W25" t="n">
+        <v>8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6365,6 +6501,12 @@
           <t>Hutnictwo żelaza</t>
         </is>
       </c>
+      <c r="Y26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6513,6 +6655,12 @@
           <t>Inżynieria</t>
         </is>
       </c>
+      <c r="Y28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6587,6 +6735,12 @@
           <t>Oblężnictwo</t>
         </is>
       </c>
+      <c r="Y29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6661,6 +6815,9 @@
           <t>Filozofia</t>
         </is>
       </c>
+      <c r="Y30" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6735,6 +6892,9 @@
           <t>Filozofia</t>
         </is>
       </c>
+      <c r="Y31" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6809,6 +6969,9 @@
           <t>Prawo</t>
         </is>
       </c>
+      <c r="Y32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6883,6 +7046,9 @@
           <t>Prawo</t>
         </is>
       </c>
+      <c r="Y33" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6957,6 +7123,9 @@
           <t>Kodeks</t>
         </is>
       </c>
+      <c r="Y34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7031,6 +7200,9 @@
           <t>Medycyna</t>
         </is>
       </c>
+      <c r="Y35" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7178,6 +7350,12 @@
         <is>
           <t>Sztuka wojenna</t>
         </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/panele-sterowania/Panel-B.xlsx
+++ b/panele-sterowania/Panel-B.xlsx
@@ -2347,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3016,20 +3016,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>prawo_ratusz</t>
+          <t>prawo_dom_starszyzny</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Ratusza (gdy wpięty w budynki).</t>
+          <t>Bonus Prawa z Domu Starszyzny — administracja lokalna miast regionalnych, poziom 1 (Kamień); 50% wartości Pałacu III (decyzja Macieja 2026-07-25, łańcuch Dom Starszyzny → Dwór Zarządcy → Pretorium, zastępowanie jak Pałac).</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=8 … hard=4</t>
+          <t>easy=36 … hard=22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3054,20 +3054,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>prawo_pretorium</t>
+          <t>prawo_dwor_zarzadcy</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Pretorium.</t>
+          <t>Bonus Prawa z Dworu Zarządcy — administracja lokalna miast regionalnych, poziom 2 (Brąz), zastępuje Dom Starszyzny; 60% wartości Pałacu III (decyzja Macieja 2026-07-25).</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=6 … hard=3</t>
+          <t>easy=43 … hard=26</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3092,20 +3092,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>prawo_sad</t>
+          <t>prawo_pretorium</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonus Prawa z Sądu.</t>
+          <t>Bonus Prawa z Pretorium — 70% wartości Pałacu III (decyzja Macieja 2026-07-25, Pytanie 28).</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=6 … hard=3</t>
+          <t>easy=50 … hard=31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>prawo_palac</t>
+          <t>prawo_trybunal</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Pałac — główne źródło Prawa (≈1,75× jednostka garnizonu; PT 2026-07).</t>
+          <t>Bonus Prawa z Trybunału — dostępny wszędzie (stolica i region), niezależny od łańcucha administracji lokalnej; 50% wartości Dworu Zarządcy (decyzja Macieja 2026-07-25). Wcześniej Trybunał w ogóle nie był wpięty w system Prawa (hasTrybunal nie istniało).</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=45 … hard=28</t>
+          <t>easy=22 … hard=13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3168,20 +3168,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prawo_kara_brak_garnizonu</t>
+          <t>prawo_sad</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
+          <t>Bonus Prawa z Sądu — 50% wartości Pretorium (decyzja Macieja 2026-07-25, Pytanie 28).</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=25 … hard=16</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3206,20 +3206,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>prawo_kara_podboj_bez_garnizonu</t>
+          <t>prawo_palac</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Kara Prawa gdy po podboju obca kultura+religia i brak jednostek w mieście. [B-KULT-REL]</t>
+          <t>Pałac I — główne źródło Prawa (≈1,75× jednostka garnizonu; PT 2026-07). Prawo z Pałacu rośnie z tierem (decyzja Macieja 2026-07-25, Pytanie 27=A) — patrz prawo_palac_ii, prawo_palac_iii.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=-2 … hard=-4</t>
+          <t>easy=45 … hard=28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3244,20 +3244,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada</t>
+          <t>prawo_palac_ii</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LEGACY — zastąpione przez prawo_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+          <t>Pałac II — Prawo rośnie z tierem Pałacu (decyzja Macieja 2026-07-25, Pytanie 27=A).</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=58 … hard=36</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3282,22 +3282,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>prawo_bonus_osiedle_pop</t>
+          <t>prawo_palac_iii</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>D-START-OSIEDLE: bonus Prawa pop 1→4. Cel PorPct T1 pop=1: easy ~75%, normal ~55%, hard ~35% (kult+rel).</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>28, 20, 14, 8</t>
-        </is>
+          <t>Pałac III — Prawo rośnie z tierem Pałacu; Pretorium = 70% tej wartości (decyzja Macieja 2026-07-25, Pytania 27=A i 28).</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>easy=[32, 24, 16, 10] … hard=[22, 16, 10, 6]</t>
+          <t>easy=71 … hard=44</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3322,25 +3320,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prawo_bonus_osada_prog</t>
+          <t>prawo_kara_brak_garnizonu</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+          <t>Kara gdy pop≥6 i brak garnizonu (opcjonalne v1.0).</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>easy=4 … hard=4</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>pkt Prawa</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3360,33 +3358,187 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>prawo_kara_podboj_bez_garnizonu</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Kara Prawa gdy po podboju obca kultura+religia i brak jednostek w mieście. [B-KULT-REL]</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>easy=-2 … hard=-4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osada</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>LEGACY — zastąpione przez prawo_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osiedle_pop</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>D-START-OSIEDLE: bonus Prawa pop 1→4. Cel PorPct T1 pop=1: easy ~75%, normal ~55%, hard ~35% (kult+rel).</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>28, 20, 14, 8</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>easy=[32, 24, 16, 10] … hard=[22, 16, 10, 6]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pkt Prawa</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prawo_bonus_osada_prog</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Populacja ≤ prog → bonus osady (D16-A).</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Prawo, garnizon</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>prawo_bonus_stolica_easy</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>D18-4 A+C: pierwsze miasto gracza na easy, T1–10.</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>easy=1 … hard=0</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>pkt Prawa</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Prawo, garnizon</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>
@@ -4261,7 +4413,7 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -4401,7 +4553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4692,10 +4844,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4706,7 +4855,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kuznia</t>
+          <t>Kuźnia brązu</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4740,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -4764,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -4772,10 +4921,10 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4786,7 +4935,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piec hutniczy</t>
+          <t>Odlewnia brązu</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4851,11 +5000,11 @@
           <t>Brązownictwo</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>6</v>
+      </c>
       <c r="X5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -4879,7 +5028,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -4931,35 +5080,35 @@
           <t>Hutnictwo żelaza</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>8</v>
+      </c>
       <c r="Y6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>targowisko</t>
+          <t>wielka_odlewnia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Targowisko (Rynek)</t>
+          <t>Wielka odlewnia</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -4983,10 +5132,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -5004,39 +5153,42 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Wymiana</t>
+          <t>Obróbka żelaza</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>targowisko</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Port handlowy</t>
+          <t>Targowisko (Rynek)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -5085,143 +5237,143 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Żegluga</t>
+          <t>Wymiana</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>port_wielki</t>
+          <t>port</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Port wielki</t>
+          <t>Port handlowy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Żegluga</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
         <v>12</v>
       </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v>6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Inżynieria</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>karawanseraj</t>
+          <t>port_wielki</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Karawanseraj</t>
+          <t>Port wielki</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -5238,15 +5390,18 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Handel</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>4</v>
+          <t>Inżynieria</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>12</v>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -5323,10 +5478,7 @@
         </is>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -5402,7 +5554,10 @@
           <t>Warzelnia soli</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="W12" t="n">
+        <v>8</v>
+      </c>
+      <c r="X12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5480,10 +5635,7 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -5560,10 +5712,10 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -5676,10 +5828,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -5700,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -5716,8 +5868,11 @@
           <t>Religia</t>
         </is>
       </c>
-      <c r="Y16" t="n">
+      <c r="W16" t="n">
         <v>6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -5793,8 +5948,11 @@
           <t>Pismo</t>
         </is>
       </c>
-      <c r="Y17" t="n">
-        <v>5</v>
+      <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -5870,7 +6028,7 @@
           <t>Gospodarka wodna</t>
         </is>
       </c>
-      <c r="X18" t="n">
+      <c r="W18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5947,7 +6105,10 @@
           <t>Budownictwo</t>
         </is>
       </c>
-      <c r="Y19" t="n">
+      <c r="W19" t="n">
+        <v>6</v>
+      </c>
+      <c r="X19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6024,112 +6185,112 @@
           <t>Waluta</t>
         </is>
       </c>
+      <c r="W20" t="n">
+        <v>6</v>
+      </c>
       <c r="X20" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mury</t>
+          <t>palisada</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mury</t>
+          <t>Palisada drewniana</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Obróbka drewna</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
         <v>12</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Budownictwo</t>
-        </is>
-      </c>
-      <c r="Y21" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koszary</t>
+          <t>mury</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Koszary</t>
+          <t>Mury</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6150,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -6174,72 +6335,69 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Wojskowość</t>
+          <t>Budownictwo</t>
         </is>
       </c>
       <c r="W22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>magazyn</t>
+          <t>koszary</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Magazyn</t>
+          <t>Koszary</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>20</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -6261,41 +6419,41 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Handel</t>
+          <t>Wojskowość</t>
         </is>
       </c>
       <c r="W23" t="n">
         <v>8</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stela</t>
+          <t>magazyn</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Stela / Pomnik</t>
+          <t>Magazyn</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -6304,22 +6462,22 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -6328,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -6341,8 +6499,11 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Murarstwo</t>
-        </is>
+          <t>Handel</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>10</v>
       </c>
       <c r="X24" t="n">
         <v>6</v>
@@ -6351,22 +6512,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>palac</t>
+          <t>stela</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palac</t>
+          <t>Stela / Pomnik</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -6381,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -6405,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -6418,189 +6579,186 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>8</v>
+          <t>Murarstwo</t>
+        </is>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kuznia_zelaza</t>
+          <t>palac</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kuźnia żelaza</t>
+          <t>Pałac</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Hutnictwo żelaza</t>
-        </is>
-      </c>
-      <c r="Y26" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>wielka_kuznia</t>
+          <t>palac_ii</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia</t>
+          <t>Pałac II</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D27" t="n">
         <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>5</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>23</v>
-      </c>
-      <c r="N27" t="n">
-        <v>9</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Obróbka żelaza</t>
-        </is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>10</v>
+      </c>
+      <c r="X27" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fort</t>
+          <t>palac_iii</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cytadela</t>
+          <t>Pałac III</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -6615,13 +6773,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -6639,42 +6797,42 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Inżynieria</t>
-        </is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>10</v>
       </c>
       <c r="Y28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>warsztat_oblezniczy</t>
+          <t>kuznia_zelaza</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warsztat oblężniczy</t>
+          <t>Kuźnia żelaza</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -6683,7 +6841,7 @@
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -6704,10 +6862,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -6728,116 +6886,119 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Oblężnictwo</t>
-        </is>
+          <t>Hutnictwo żelaza</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>akademia</t>
+          <t>wielka_kuznia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akademia</t>
+          <t>Wielka Kuźnia</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D30" t="n">
+        <v>18</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>15</v>
       </c>
-      <c r="E30" t="n">
+      <c r="N30" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>10</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Filozofia</t>
-        </is>
+          <t>Obróbka żelaza</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>teatr</t>
+          <t>fort</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Teatr</t>
+          <t>Cytadela</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -6852,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6876,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -6889,38 +7050,41 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Filozofia</t>
-        </is>
-      </c>
-      <c r="Y31" t="n">
+          <t>Inżynieria</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
         <v>10</v>
+      </c>
+      <c r="X31" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>baszta</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sąd</t>
+          <t>Baszta</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6929,10 +7093,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6944,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6956,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -6966,26 +7130,29 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Prawo</t>
-        </is>
-      </c>
-      <c r="Y32" t="n">
-        <v>8</v>
+          <t>Inżynieria</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>10</v>
+      </c>
+      <c r="X32" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pretorium</t>
+          <t>warsztat_oblezniczy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pretorium</t>
+          <t>Warsztat oblężniczy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -6994,11 +7161,11 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
-        <v>3</v>
-      </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
@@ -7009,20 +7176,20 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>10</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -7033,81 +7200,84 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Prawo</t>
-        </is>
-      </c>
-      <c r="Y33" t="n">
-        <v>9</v>
+          <t>Oblężnictwo</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>10</v>
+      </c>
+      <c r="X33" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>trybunal</t>
+          <t>akademia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trybunał</t>
+          <t>Akademia</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>10</v>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -7116,30 +7286,33 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Kodeks</t>
-        </is>
+          <t>Filozofia</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>laznia_publiczna</t>
+          <t>teatr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Łaźnia publiczna</t>
+          <t>Teatr</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D35" t="n">
         <v>12</v>
@@ -7154,13 +7327,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
@@ -7178,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -7197,8 +7370,11 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Medycyna</t>
-        </is>
+          <t>Filozofia</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>8</v>
       </c>
       <c r="Y35" t="n">
         <v>10</v>
@@ -7207,12 +7383,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lazaret</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lazaret</t>
+          <t>Sąd</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7228,37 +7404,37 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7270,92 +7446,495 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Medycyna</t>
-        </is>
+          <t>Prawo</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>dom_starszyzny</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dom Starszyzny</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>25</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dwor_zarzadcy</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Dwór Zarządcy</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>45</v>
+      </c>
+      <c r="D38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Kodeks</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>6</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>pretorium</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pretorium</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>75</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Prawo</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>trybunal</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Trybunał</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Kodeks</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>6</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>laznia_publiczna</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Łaźnia publiczna</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>50</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medycyna</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>akademia_wojskowa</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Akademia wojskowa</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C42" t="n">
         <v>80</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D42" t="n">
         <v>18</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E42" t="n">
         <v>4</v>
       </c>
-      <c r="F37" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>20</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N42" t="n">
         <v>2</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>6</v>
-      </c>
-      <c r="V37" t="inlineStr">
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="inlineStr">
         <is>
           <t>Sztuka wojenna</t>
         </is>
       </c>
-      <c r="Y37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>6</v>
+      <c r="W42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7369,7 +7948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -7434,7 +8013,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>budulec; wejscie Tartaku i konwerterow (Cegielnia/Garncarnia/Piec hutniczy/Odlewnia zelaza/Wielka Kuznia) 1:1 zamiast dawnego Paliwa</t>
+          <t>budulec; wejscie Tartaku i konwerterow (Cegielnia/Garncarnia/Odlewnia brązu/Odlewnia żelaza/Wielka odlewnia) 1:1 zamiast dawnego Paliwa</t>
         </is>
       </c>
     </row>
@@ -7539,12 +8118,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>złoże Konie / Stajnia (później)</t>
+          <t>Stadnina (złoże konia) + szlaki handlowe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Konnica (Brąz) i rydwany konne; NIEDOSTĘPNY u Majów/Ameryki (konie wyginęły w Nowym Świecie ~10 000 p.n.e.)</t>
+          <t>magazyn państwa (klucz stock: kon); Stadnina 1/t; rekrut jednostek Typ Mount +5 Koni (U-15); NIEDOSTĘPNY u Majów/Ameryki Pd.</t>
         </is>
       </c>
     </row>
@@ -7561,41 +8140,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>złoże Sól (wybrzeże) + Warzelnia soli</t>
+          <t>Warzelnia soli (wybrzeże / złoże sol) + szlaki handlowe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bramka Spichlerz II; konserwacja żywności</t>
+          <t>magazyn państwa (klucz stock: sol); Warzelnia 10/t; zużycie Spichlerz II (5 Sól/t × działający)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cegła</t>
+          <t>Złoto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>przetworzony</t>
+          <t>surowy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cegielnia (glina+drewno)</t>
+          <t>Kopalnia złota + szlaki handlowe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>budulec</t>
+          <t>magazyn państwa (klucz stock: zloto) ≠ Pieniądz (skarbiec); Kopalnia 1/t; Mennica zużywa 1 Złoto/t w stolicy przy mnożniku handlu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ceramika</t>
+          <t>Cegła</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7605,19 +8184,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Garncarnia (glina+drewno)</t>
+          <t>Cegielnia (glina+drewno)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+zadowolenie, +Zdrowie</t>
+          <t>budulec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brąz</t>
+          <t>Ceramika</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7627,56 +8206,78 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piec hutniczy (ruda+drewno)</t>
+          <t>Garncarnia (glina+drewno)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>budulec + jednostki brazowe</t>
+          <t>magazyn państwa (klucz stock: ceramika); zużycie Spichlerz I/II (5 Ceramiki/t); Garncarnia nie zużywa Ceramiki (U-14)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Żelazo</t>
+          <t>Brąz</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>surowy</t>
+          <t>przetworzony</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>złoże Ruda żelaza + Kuźnia żelaza</t>
+          <t>Odlewnia brązu (ruda+drewno)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>model dostępu v0.1 = boolean (złoże w zasięgu + ulepszenie); odblokowuje tech Hutnictwo żelaza; prereq Kuźni żelaza</t>
+          <t>budulec + jednostki brazowe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Żelazo</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>surowy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Odlewnia żelaza (ruda żelaza+drewno)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>dostęp: Kopalnia żelaza (mapa) + Odlewnia żelaza (miasto); odblokowuje tech Hutnictwo żelaza; Kuźnia żelaza = osobny slot (pancerz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Stal</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>przetworzony</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Wielka Kuźnia (żelazo+drewno)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>odblokowuje tech Obróbka żelaza; prereq Wielkiej Kuźni; model dostępu v0.1 = boolean</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wielka odlewnia (żelazo+drewno)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>odblokowuje tech Obróbka żelaza; Wielka Kuźnia = tylko pancerz (+45% łańcuch kuźni), bez produkcji stali</t>
         </is>
       </c>
     </row>
@@ -7782,11 +8383,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Stolarnia</t>
+          <t>Stolarnia; Palisada drewniana</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -7806,7 +8407,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -7829,7 +8430,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -7849,7 +8450,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -7872,7 +8473,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7900,11 +8501,11 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B1-Q2A Maciej 2026-06-29; T-TECH-4: Tarasy po Rolnictwie</t>
+          <t>B1-Q2A Maciej 2026-06-29; T-TECH-4: Tarasy po Rolnictwie; tier-1 Kamień: 5/10/20 PN (szybka/std/dluga)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7933,11 +8534,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>B1-Q2A Maciej 2026-06-29</t>
+          <t>B1-Q2A Maciej 2026-06-29; tier-1 Kamień: 5/10/20 PN (szybka/std/dluga)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7958,7 +8559,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7976,7 +8577,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -8009,7 +8610,12 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>tier-1 Kamień: 5/10/20 PN (szybka/std/dluga)</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8029,7 +8635,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -8042,7 +8648,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8075,7 +8681,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -8103,7 +8709,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8123,7 +8729,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8146,7 +8752,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -8180,11 +8786,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Odlewnia brązu; Kuznia; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
+          <t>Odlewnia brązu; Kuźnia brązu; Jednostki: Włócznik, Wojownik z mieczem i tarczą, Impi, Wojownik z toporem, Wojownik z khopesh, Włócznik sumeryjski, Wojownik mykeński, Wojownik Sherden, Halabardnik Shang, Wieża oblężnicza, Wojownik tyrreński, Wojownik szekelesz</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -8227,7 +8833,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -8270,7 +8876,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -8308,7 +8914,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -8346,7 +8952,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>56</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -8374,7 +8980,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -8402,7 +9008,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -8436,11 +9042,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Karawanseraj; Magazyn</t>
+          <t>Magazyn</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -8464,11 +9070,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Trybunał</t>
+          <t>Trybunał; Dwór Zarządcy</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
@@ -8501,7 +9107,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -8539,11 +9145,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>kończy Epokę 2 (Pieniądz); T-TECH-6: Mennica v1.0</t>
+          <t>kończy Epokę 2 (Pieniądz); T-TECH-6: Mennica v1.0; ZLOTO 2026-07-25: Mennica dodatkowo wymaga dostępu do Złota (Kopalnia złota) + Targowiska w mieście</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Kopalnia złota</t>
         </is>
       </c>
     </row>
@@ -8572,7 +9183,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8601,7 +9212,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Piec hutniczy</t>
+          <t>Odlewnia brązu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8616,15 +9227,15 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kuźnia żelaza; Jednostki: Hastati, Falanga, Drużynnik, Garnizon Harappy, Gwardia hetycka, Piechota neobabilońska, Tyrski miecznik, Gwardia Tyreńska, Thorakites, iButho z iklwa, Wojownik z żelaznym khopesh, Mur tarcz (Sargonid), Miecznik galijski, Rydwan celtycki, Konnica lancowa asyryjska, Konnica łucznicza asyryjska, Jeździec z oszczepami</t>
+          <t>Odlewnia żelaza; Kuźnia żelaza; Jednostki: Hastati, Falanga, Drużynnik, Garnizon Harappy, Gwardia hetycka, Piechota neobabilońska, Tyrski miecznik, Gwardia Tyreńska, Thorakites, iButho z iklwa, Wojownik z żelaznym khopesh, Mur tarcz (Sargonid), Miecznik galijski, Rydwan celtycki, Konnica lancowa asyryjska, Konnica łucznicza asyryjska, Jeździec z oszczepami</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>kończy Epokę 2 / otwiera Epokę 3; jednostki żelazne (Gaesatae, Soldurii, Wojownik germański itp.) — do zdefiniowania przez UNITS; Kuźnia żelaza = NOWY budynek dla EKONOMIA</t>
+          <t>kończy Epokę 2 / otwiera Epokę 3; Odlewnia żelaza = upgrade Odlewni brązu (brąz+żelazo); Kuźnia żelaza = łańcuch pancerza (osobny slot)</t>
         </is>
       </c>
     </row>
@@ -8649,15 +9260,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fort</t>
+          <t>Fort; Cytadela; Baszta</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fort = NOWY budynek (obrona terenu, zasięg 10, +100% obrona przy obozowaniu — zob. civ-bonusy-obronne-mapa.md); Akwedukt ulepszony = rozszerzenie istniejącego Akweduktu</t>
+          <t>Fort = NOWY budynek (obrona terenu, zasięg 10, +100% obrona przy obozowaniu — zob. civ-bonusy-obronne-mapa.md); Akwedukt ulepszony = rozszerzenie istniejącego Akweduktu. Baszta (decyzja 41B, 2026-07-25) -- trzeci budynek obronny miasta, obok Cytadeli, ta sama technologia.</t>
         </is>
       </c>
     </row>
@@ -8691,7 +9302,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -8729,7 +9340,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -8762,7 +9373,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8790,7 +9401,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8833,7 +9444,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8877,15 +9488,15 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia; Jednostki: Gaesatae, Soldurii, Wojownik germański, Berserker germański</t>
+          <t>Wielka odlewnia; Wielka Kuźnia; Jednostki: Gaesatae, Soldurii, Wojownik germański, Berserker germański</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Wielka Kuźnia = NOWY budynek (produkcja++, mnoznik jednostek++); stal = NOWY surowiec dla DANE (prereq dalszych epok); EKONOMIA dodaje surowiec; UNITS aktualizuje jednostki żelazne wyższego poziomu</t>
+          <t>Wielka odlewnia = produkcja stal+metale (brąz+żelazo+stal); Wielka Kuźnia = tylko pancerz +45% łańcuch kuźni; stal = NOWY surowiec dla DANE (prereq dalszych epok)</t>
         </is>
       </c>
     </row>
@@ -8919,7 +9530,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8999,7 +9610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9069,7 +9680,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -9094,21 +9705,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>budynek_mnoznik_poziomu</t>
+          <t>jednostka_koszt_ludnosci</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Mnoznik compound (procent skladany) efektu I kosztu budynku za kazdy poziom: wartosc^(poziom-1). Decyzja Naster = +10%/epoke. Uzywany w production.itemCost (koszt) i buildingEffectAtLevel (efekt).</t>
+          <t>Koszt ludnosci miasta za ukonczenie jednostki z kolejki (rekrutacja). USTAWIONE 0 (Maciej 2026-07-21): rekrutacja NIE zabiera juz populacji miasta — jedynym kosztem werbu jest pula Manpower (epoka-ludnosc-manpower.json / manpower.ts). production.populationCostOf; przy 0 populacja pozostaje bez zmian.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>x / poziom</t>
+          <t>ludnosc</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -9128,21 +9739,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jednostka_koszt_ludnosci</t>
+          <t>manpower_regen_proc_max_tura</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Koszt ludnosci miasta za ukonczenie jednostki z kolejki (rekrutacja). USTAWIONE 0 (Maciej 2026-07-21): rekrutacja NIE zabiera juz populacji miasta — jedynym kosztem werbu jest pula Manpower (epoka-ludnosc-manpower.json / manpower.ts). production.populationCostOf; przy 0 populacja pozostaje bez zmian.</t>
+          <t>Co koniec tury miasto odzyskuje floor(manpowerMax × wartosc/100) Manpower (do cap). Ep1, 10 ludkow, max=10k → +200/ture. Pusta pula ≈50 tur do pelna. manpower.tickManpowerRegen.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ludnosc</t>
+          <t>% max/ture</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -9162,21 +9773,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>manpower_regen_proc_max_tura</t>
+          <t>manpower_regen_blok_oblezenie</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Co koniec tury miasto odzyskuje floor(manpowerMax × wartosc/100) Manpower (do cap). Ep1, 10 ludkow, max=10k → +200/ture. Pusta pula ≈50 tur do pelna. manpower.tickManpowerRegen.</t>
+          <t>1 = brak odnowy Manpower gdy city.oblegane=true. 0 = regen normalnie podczas oblężenia.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>% max/ture</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -9196,21 +9807,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>manpower_regen_blok_oblezenie</t>
+          <t>manpower_uzupelnienie_hp_proc_max_tura</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1 = brak odnowy Manpower gdy city.oblegane=true. 0 = regen normalnie podczas oblężenia.</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
+          <t>Co koniec tury (po odnowie puli Manpower): jednostka wojskowa leczy floor(maxHP × wartość/100) HP z puli imperium. Koszt MP = ceil(healHp/maxHP × kosztJednostki). Przy braku MP — leczenie częściowe do dostępnej puli. manpower.tickManpowerUnitReplenishment.</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>% maxHP/tura</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -9575,7 +10183,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Miasto Z MUREM daje +200% Obrony broniacym sie jednostkom (bitwa/oblezenie). Decyzja Naster 2026-06-25. Konsumuje game/siege.ts + battleScene (defensa miasta). Miasto bez muru = brak tego bonusu.</t>
+          <t>Miasto Z MUREM (budynek 'mury', City.maMur) daje +200% Obrony broniacym sie jednostkom (bitwa/oblezenie). Decyzja Naster 2026-06-25. Konsumuje main.ts structureDefenseBonusFor -&gt; combat.ts structureDefBonusPct + battleScene.ts (onWallWalkway). Miasto bez muru = brak tego bonusu. Miasto z Cytadela (upgrade Murow, patrz bonus_obrona_cytadela_proc) dostaje ten bonus RAZEM z dodatkowym -- lacznie +300%, nie osobnymi warstwami w kodzie (jeden zwracany procent: 200 albo 300).</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -9604,21 +10212,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>zasieg_okolicy_baza</t>
+          <t>bonus_obrona_cytadela_proc</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Minimalny promien okolicy przy populacji 1..4 (start miasta = 5 heksow). Czytane przez okolica.cityRangeForPopulation (Maciej 2026-06-27).</t>
+          <t>Miasto z Cytadela (budynek 'fort' -- UWAGA: to jest budynek Cytadela, upgrade Murow; NIE mylic z ulepszeniem terenowym 'fort' na mapie, ktore daje osobny bonus +100% dla obozujacych jednostek poza miastem) daje DODATKOWE +100% Obrony PONAD bonus muru -- lacznie +300% (200 mur + 100 cytadela). Decyzja Maciej 2026-07-25: "3, 100%. Bo to juz by bylo za duzo, i tak z murami jest 300%." Cytadela to upgrade budynku 'mury' (ID podmieniane w cityBuilt), wiec miasto z Cytadela NIE ma juz 'mury' w liscie budynkow -- flaga City.maMur pozostaje true (main.ts ustawia ja dla obu ID), a rozroznienie mur/cytadela robi structureDefenseBonusFor po cityBuilt.includes('fort'). Konsumuje main.ts structureDefenseBonusFor -&gt; combat.ts structureDefBonusPct + battleScene.ts (onWallWalkway).</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pola/strona</t>
+          <t>% Obrony (dodatkowo do muru)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -9638,21 +10246,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>zasieg_okolicy_pop5</t>
+          <t>bonus_obrona_baszta_proc</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>[LEGACY - nieuzywane od 2026-06-25] Zasieg okolicy przy populacji &gt;= 5 (stary model schodkowy). Zachowane dla wstecznej zgodnosci parsowania.</t>
+          <t>Decyzja 41B (Maciej 2026-07-25): Baszta -- TRZECI, niezalezny budynek obronny (buildings.json id='baszta'), dokladany obok Murow i Cytadeli (brak upgradeFrom, zaden nie zastepuje pozostalych). Daje DODATKOWE +100% Obrony PONAD Mury (+200%) i Cytadele (+100%) -- miasto z kompletem trzech budowli obronnych = +400% lacznie (200 mur + 100 cytadela + 100 baszta). Konsumuje main.ts structureDefenseBonusFor -&gt; game/city-defense.ts cityWallDefenseBonusPercent -&gt; combat.ts structureDefBonusPct + battleScene.ts (onWallWalkway). Baszta sama (bez Murow/Cytadeli) daje WYLACZNIE swoj wlasny +100% -- baza 'mur' (200%) aktywuje sie tylko gdy w miescie stoi realnie budynek 'mury' lub 'fort'.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pola/strona</t>
+          <t>% Obrony (dodatkowo do muru+cytadeli)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -9672,21 +10280,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>zasieg_okolicy_pop10</t>
+          <t>bonus_obrona_palisada_proc</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>[LEGACY - nieuzywane od 2026-06-25] Zasieg okolicy przy populacji &gt;= 10 (stary model schodkowy). Zachowane dla wstecznej zgodnosci parsowania.</t>
+          <t>Palisada drewniana (buildings.json id='palisada') -- wczesna obrona miasta przed Mury kamienne: +100% Obrony broniącym się jednostkom. Epoka Kamienia, tech Obróbka drewna. Mury (+200%) ZASTĘPUJĄ bonus palisady (nie stackują -- patrz game/city-defense.ts). Konsumuje main.ts structureDefenseBonusFor -&gt; cityWallDefenseBonusPercent -&gt; combat.ts structureDefBonusPct + battleScene.ts (onWallWalkway). Odblokowuje City.maMur (jak Mury) dla bramki terenu przy obronie miasta.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pola/strona</t>
+          <t>% Obrony (wczesna palisada drewniana)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -9706,21 +10314,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>udzial_output_produkcja</t>
+          <t>zasieg_okolicy_baza</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Domyslny udzial outputu miasta kierowany do strumienia PRODUKCJA. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+          <t>Minimalny promien okolicy przy populacji 1..4 (start miasta = 5 heksow). Czytane przez okolica.cityRangeForPopulation (Maciej 2026-06-27).</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>udzial [0..1]</t>
+          <t>pola/strona</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -9740,21 +10348,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>udzial_output_pieniadz</t>
+          <t>zasieg_okolicy_pop5</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Domyslny udzial outputu miasta kierowany do strumienia PIENIADZ. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+          <t>[LEGACY - nieuzywane od 2026-06-25] Zasieg okolicy przy populacji &gt;= 5 (stary model schodkowy). Zachowane dla wstecznej zgodnosci parsowania.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>udzial [0..1]</t>
+          <t>pola/strona</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -9774,21 +10382,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>udzial_output_nauka</t>
+          <t>zasieg_okolicy_pop10</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Domyslny udzial outputu miasta kierowany do strumienia NAUKA. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+          <t>[LEGACY - nieuzywane od 2026-06-25] Zasieg okolicy przy populacji &gt;= 10 (stary model schodkowy). Zachowane dla wstecznej zgodnosci parsowania.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2</v>
+        <v>15</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>udzial [0..1]</t>
+          <t>pola/strona</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -9808,16 +10416,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>udzial_output_rozwoj</t>
+          <t>udzial_output_produkcja</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Domyslny udzial outputu miasta kierowany do strumienia ROZWOJ. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+          <t>Domyslny udzial outputu miasta kierowany do strumienia PRODUKCJA. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
@@ -9831,6 +10439,108 @@
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>miasto-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>udzial_output_pieniadz</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Domyslny udzial outputu miasta kierowany do strumienia PIENIADZ. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>udzial [0..1]</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>miasto-params → production, cities, okolica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>miasto-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>udzial_output_nauka</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Domyslny udzial outputu miasta kierowany do strumienia NAUKA. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>udzial [0..1]</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>miasto-params → production, cities, okolica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>miasto-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>udzial_output_rozwoj</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Domyslny udzial outputu miasta kierowany do strumienia ROZWOJ. production.DEFAULT_OUTPUT_SHARES / splitOutput.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>udzial [0..1]</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>miasto-params → production, cities, okolica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>miasto-params.json</t>
         </is>
@@ -9847,7 +10557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10217,7 +10927,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Nauka (= BADANIA) w podziale Handlu netto. Default 20% (Maciej 2026-06-25).</t>
+          <t>Domyślny udział strumienia Nauka (= BADANIA) w podziale Daniny netto nowego miasta. 20% (Maciej 2026-06-25, potwierdzone przy decyzji 74 = A z 2026-07-25 — ten strumień zostaje bez zmian).</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10230,7 +10940,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% Daniny netto miasta (po Walucie i Mennicy: Podatku netto)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -10255,20 +10965,20 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Pieniądz (= SKARBIEC/podatek) w podziale Handlu netto. Default 70% (Maciej 2026-06-25).</t>
+          <t>Domyślny udział strumienia Pieniądz (= SKARBIEC) w podziale Daniny netto nowego miasta. Obniżony 70% → 60% decyzją Maciej 2026-07-25 (PYTANIE 74 = A); te 10 punktów procentowych przeszło na Zamożność, żeby nowe miasto nie startowało z ujemnym Szczęściem na trudnym.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=70 … hard=70</t>
+          <t>easy=60 … hard=60</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% Daniny netto miasta (po Walucie i Mennicy: Podatku netto)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -10293,20 +11003,20 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Domyślny udział strumienia Zamożność (Wealth) w podziale Handlu netto. Default 10% (Maciej 2026-06-25). Luksus ≠ surowiec — osobna kategoria elitarna (poza grą v1).</t>
+          <t>Domyślny udział strumienia Zamożność (Wealth) w podziale Daniny netto nowego miasta. Podniesiony 10% → 20% decyzją Maciej 2026-07-25 (PYTANIE 74 = A). Powód: 20% to dokładnie próg utrzymania poziomu Zamożności (20% pieniądza miasta przy poziomie 0), więc poziom Zamożności rusza z miejsca bez ręcznej interwencji; w nowej siatce Szczęścia przedział 20-29% daje +1 pkt Szczęścia na normalnym i 0 na trudnym (zamiast 0 / -1 przy dawnych 10%).</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=10 … hard=10</t>
+          <t>easy=20 … hard=20</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% Daniny netto miasta (po Walucie i Mennicy: Podatku netto)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -10445,7 +11155,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Atrycja HP jednostek na mapie gdy zapasy państwa &lt; 0 po koszcie armii (−8% maxHP/tura normal).</t>
+          <t>Atrycja HP jednostek na mapie gdy zapasy państwa &lt; 0 po koszcie armii, PO karencji glod_wojska_karencja_tur (−8% maxHP/tura normal). Identycznie dla gracza i AI (parytet, Maciej 2026-07-26).</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10478,25 +11188,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>spichlerz_pojemnosc_zapasow_panstwa</t>
+          <t>glod_wojska_karencja_tur</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Max zapasów armii na 1 Spichlerz w imperium (100% odkładania). Suma = wartość × liczba Spichlerzy. Bez Spichlerza: odkładanie 50%, bez limitu pojemności.</t>
+          <t>C-GLOD-Q1=A (Maciej 2026-07-26, wariant A): liczba kolejnych tur Z RZĘDU z ujemnymi zapasami państwa, zanim ruszy atrycja HP wojska (glod_wojska_hp_frac). Domyślny suwak żywności (suwak_zywnosc_rozwoj_domyslnie) NIE zmieniony przy tej decyzji. Bez różnicowania między poziomami trudności — sama karencja to 3 tury wszędzie.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=120 … hard=80</t>
+          <t>easy=3 … hard=3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🍞</t>
+          <t>tury</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -10516,25 +11226,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>armia_odklad_bez_spichlerza</t>
+          <t>glod_wojska_stat_mult</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Od startu gry: ułamek netto żywności armii (po koszcie wojska) odkładany do zapasów państwa BEZ Spichlerza w imperium. Reszta przepada.</t>
+          <t>Mnożnik parametrów bojowych (bez armor) gdy zapasy państwa &lt; 0 po koszcie armii — jednostka osłabiona zanim ruszy atrycja HP.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=0.6 … hard=0.4</t>
+          <t>easy=0.75 … hard=0.75</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ułamek</t>
+          <t>mnożnik</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -10554,12 +11264,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>armia_odklad_ze_spichlerzem</t>
+          <t>zywnosc_mnoznik_terytorium_wlasne</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Ułamek netto żywności armii odkładany do zapasów państwa gdy w imperium jest ≥1 Spichlerz (100%). Limit pojemności = spichlerz_pojemnosc × liczba Spichlerzy.</t>
+          <t>C-GLOD-Q2=B (Maciej 2026-07-26): mnożnik zużycia żywności jednostki wojskowej stojącej na WŁASNYM terytorium (bez zmian względem stawki bazowej zywnosc_jednostka_ruch/oboz).</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10567,12 +11277,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=1 … hard=1</t>
+          <t>easy=1.0 … hard=1.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ułamek</t>
+          <t>mnożnik</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -10592,12 +11302,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>korupcja_wspolczynnik_dystansu</t>
+          <t>zywnosc_mnoznik_poza_terytorium</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Strata% += Dystans_od_Stolicy × wartość. Im większy, tym dotkliwsza korupcja. [PT]</t>
+          <t>C-GLOD-Q2=B (Maciej 2026-07-26, wariant uproszczony): mnożnik zużycia żywności jednostki wojskowej stojącej POZA własnym terytorium — bez rozróżniania dróg, ziemi niczyjej, murów ani liczby jednostek w stosie (decyzja właściciela: prosty wariant).</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10605,12 +11315,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=1 … hard=3</t>
+          <t>easy=2.0 … hard=2.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>per pole</t>
+          <t>mnożnik</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -10630,25 +11340,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>korupcja_wspolczynnik_miast</t>
+          <t>spichlerz_pojemnosc_zapasow_panstwa</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Strata% += Liczba_Miast × wartość. Każde nowe miasto podnosi korupcję globalnie. [PT]</t>
+          <t>Max zapasów armii na 1 Spichlerz w imperium (100% odkładania). Suma = wartość × liczba Spichlerzy. Bez Spichlerza: odkładanie 50%, bez limitu pojemności.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=120 … hard=80</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>per miasto</t>
+          <t>🍞</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -10668,33 +11378,413 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>armia_odklad_bez_spichlerza</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Od startu gry: ułamek netto żywności armii (po koszcie wojska) odkładany do zapasów państwa BEZ Spichlerza w imperium. Reszta przepada.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>easy=0.6 … hard=0.4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ułamek</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>armia_odklad_ze_spichlerzem</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>NIEUŻYWANE (PYTANIE-85) — stary model suwaka żywności. Zostawione dla zgodności zapisów.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ułamek</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>racje_zywnosc_1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: koszt racji poziom 1 (żywność na mieszkańca/turę). Balans 2026-07-29: 2 (było 1).</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>easy=2 … hard=2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>żywność/turę/os.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>racje_zywnosc_2</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: koszt racji poziom 2. Balans 2026-07-29: 4 (było 2).</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>easy=4 … hard=4</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>żywność/turę/os.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>racje_zywnosc_3</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: koszt racji poziom 3. Balans 2026-07-29: 6 (było 3).</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=6</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>żywność/turę/os.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>racje_wzrost_proc_1</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: bonus wzrostu z racji poziom 1.</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>easy=3 … hard=3</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>% WZROST/turę</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>racje_wzrost_proc_2</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: bonus wzrostu z racji poziom 2.</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>easy=5 … hard=5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>% WZROST/turę</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>racje_wzrost_proc_3</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-85: bonus wzrostu z racji poziom 3.</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>easy=7 … hard=7</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>% WZROST/turę</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>korupcja_wspolczynnik_dystansu</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Korupcja — współczynnik dystansu. Strata% Daniny (po wynalezieniu Waluty: Podatku) += Dystans_od_Stolicy [pola] × wartość. NIE dotyczy Pracy (decyzja Maciej 2026-07-25: korupcja obciąża wyłącznie Daninę/Podatek). Wartości obniżone o 50% wobec pierwotnych 1 / 2 / 3 (decyzja Maciej 2026-07-25: „zbyt rygorystyczne… mają mieć wpływ, ale nie być druzgocące"). [PT]</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>easy=0.5 … hard=1.5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>punkty procentowe straty Daniny/Podatku na każde pole odległości od stolicy</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>korupcja_wspolczynnik_miast</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Korupcja — współczynnik liczby miast. Strata% Daniny (po Walucie: Podatku) += Liczba_Miast × wartość; obciąża każde miasto, także stolicę. NIE dotyczy Pracy. Wartości obniżone o 50% wobec pierwotnych 1 / 1 / 2 (decyzja Maciej 2026-07-25). [PT]</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>easy=0.5 … hard=1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>punkty procentowe straty Daniny/Podatku na każde miasto w imperium</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>turn-economy, HUD suwaki</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>korupcja_cap</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Maksymalna strata z tytułu korupcji/marnotrawstwa (cap = 50%). [PT]</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Korupcja — sufit straty. Górne ograniczenie łącznej straty z dystansu i liczby miast. BEZ ZMIAN 2026-07-25 — Maciej obniżył o 50% dwa WSPÓŁCZYNNIKI (dystansu i miast), sufitu nie wymieniał; po obniżce sufit i tak jest praktycznie nieosiągalny (normal wymaga Dystans + 0,5×Liczba_Miast ≥ 50). [PT]</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>50</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>easy=38 … hard=62</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>% — maksymalna strata Daniny/Podatku w jednym mieście</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>turn-economy, HUD suwaki</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -11119,7 +12209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11223,7 +12313,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik Mennicy (Handel→Pieniądz) aktywny TYLKO gdy Mennica zbudowana ORAZ technologia Waluta odkryta w mieście. Wartości właściciela (Q5=A, 2026-07-20): easy ×2 / normal ×1,5 / hard ×1 (hard = bez bonusu, ale nie zeruje dochodu). Wcześniej 1.88/1.5/1.12 mimo że mennicaMnoznik był zahardkodowany na 1 w turn-economy.ts (Mennica nic nie robiła) — naprawione E1 zadanie 1.</t>
+          <t>JEDYNY mnożnik Handlu netto (decyzja Maciej 2026-07-25, wątek 'scalenie mnożników'): mnoży CAŁY handelNetto miasta (Skarb + Nauka + Zamożność razem, PRZED podziałem suwakiem) aktywny TYLKO gdy technologia Waluta jest odkryta ORAZ Mennica jest zbudowana w tym mieście (bramka AND — sam tech Waluty już NIE wystarcza). Wartości właściciela: easy ×2,0 / normal ×1,5 / hard ×1,0 (hard = brak efektu, nie zeruje dochodu). Poprzednio (do 2026-07-24) istniały DWA osobne mnożniki: `budynki.waluta_mnoznik` (×2 na cały Handel przy samym techu, bez Mennicy) + ten parametr (mnożył TYLKO strumień Pieniądza). Oba zostały scalone w ten jeden efekt — `waluta_mnoznik` zostaje w pliku oznaczony jako nieużywany.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11337,15 +12427,15 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>SUROW-CIV-01 (decyzja Macieja 2026-07-24): ZMIANA SEMANTYKI — od teraz to baza pojemności CAŁEGO PAŃSTWA (civ-wide, suma po wszystkich miastach ownera) per typ surowca, przy 0 zbudowanych budynków „Magazyn” w imperium — NIE per-miasto jak dawniej. Model ADDYTYWNY razem z magazyn_bonus_surowce_na_budynek (nie mnożnikowy). Placeholder do strojenia; wartości easy/normal/hard zachowują dawną proporcję 1,2/1/0,8. Dotyczy WYŁĄCZNIE surowców (drewno/kamień/glina/ruda/ruda_zelaza/cegła/brąz/żelazo/stal) — Żywność/Spichlerz nadal używa modelu mnożnikowego per-miasto (bez zmian, patrz magazyn_baza_zywnosc).</t>
+          <t>SUROW-CIV-01 (decyzja Macieja 2026-07-24): ZMIANA SEMANTYKI — od teraz to baza pojemności CAŁEGO PAŃSTWA (civ-wide, suma po wszystkich miastach ownera) per typ surowca, przy 0 zbudowanych budynków „Magazyn” w imperium — NIE per-miasto jak dawniej. Model ADDYTYWNY razem z magazyn_bonus_surowce_na_budynek (nie mnożnikowy). BAZA PODNIESIONA 100→500 (Maciej 2026-07-24), potem 500→1000 (Maciej 2026-07-28). Cap per typ = 1000 + 100 × liczba Magazynów (każdy Magazyn w dowolnym mieście dokłada +100, nie jednorazowo). Płaskie na easy/normal/hard. Dotyczy WYŁĄCZNIE surowców (drewno/kamień/glina/ruda/ruda_zelaza/cegła/brąz/żelazo/stal) — Żywność/Spichlerz nadal używa modelu mnożnikowego per-miasto (bez zmian, patrz magazyn_baza_zywnosc).</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=100 … hard=100</t>
+          <t>easy=1000 … hard=1000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -11408,25 +12498,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>magazyn_mnoznik_spichlerz</t>
+          <t>magazyn_centralny_baza_zywnosc</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik pojemności ŻYWNOŚCI przy wybudowanym Spichlerzu (magazyn_baza_zywnosc × ten mnożnik). SUROW-CIV-01 2026-07-24: surowce (drewno/kamień/…) NIE używają już tego mnożnika — patrz magazyn_baza_surowce/magazyn_bonus_surowce_na_budynek (model addytywny, civ-wide). [PT]</t>
+          <t>PYTANIE-85-Q6: baza capu centralnego magazynu żywności imperium (+ Spichlerze lokalne +100/+150, Magazyn +100). Podniesione 500→1000 (Maciej 2026-07-28).</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=6 … hard=4</t>
+          <t>easy=1000 … hard=1000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>🍞</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -11446,25 +12536,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>utrzymanie_jednostka_standard</t>
+          <t>magazyn_centralny_bonus_zywnosc_na_budynek</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Koszt utrzymania standardowej jednostki wojskowej. [PT]</t>
+          <t>PYTANIE-85: dodatek capu centralnego magazynu żywności za każdy budynek Magazyn w imperium.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=1 … hard=2</t>
+          <t>easy=100 … hard=100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pieniądz/turę</t>
+          <t>🍞 / Magazyn</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -11484,35 +12574,377 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>magazyn_mnoznik_spichlerz</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Mnożnik pojemności ŻYWNOŚCI przy wybudowanym Spichlerzu (magazyn_baza_zywnosc × ten mnożnik). SUROW-CIV-01 2026-07-24: surowce (drewno/kamień/…) NIE używają już tego mnożnika — patrz magazyn_baza_surowce/magazyn_bonus_surowce_na_budynek (model addytywny, civ-wide). [PT]</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>easy=6 … hard=4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>utrzymanie_jednostka_standard</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Koszt utrzymania standardowej jednostki wojskowej. [PT]</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=2</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pieniądz/turę</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ai_rush_jednostka_rezerwa_zlota</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-KUP-JEDN (Maciej 2026-07-24, parytet AI): bufor skarbca AI, ktory musi zostac PO zaplaceniu za rush-zakup jednostki za zloto (shouldAIRushBuyUnit, game/ai.ts) -- AI kupuje tylko gdy treasury &gt;= wartosc + koszt jednostki. Ta sama wartosc na wszystkich trudnosciach. PLACEHOLDER do strojenia (przeniesione z main.ts AI_UNIT_GOLD_RUSH_RESERVE, wartosc bez zmian).</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>easy=100 … hard=100</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Złoto</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ai_rush_jednostka_max_na_ture</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-KUP-JEDN (Maciej 2026-07-24, parytet AI): twardy cap liczby rush-zakupow jednostek za zloto na jednego AI-ownera w jednej turze (shouldAIRushBuyUnit, game/ai.ts) -- zapobiega farmieniu skarbca. Ta sama wartosc na wszystkich trudnosciach. PLACEHOLDER do strojenia (przeniesione z main.ts AI_UNIT_GOLD_RUSH_MAX_PER_TURN, wartosc bez zmian).</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>easy=1 … hard=1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>szt./ownera/turę</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ai_suwaki_deficyt_zywnosc_prog</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-SUWAKI (Maciej 2026-07-26, C-AI-SUWAKI=A): próg zapasów Żywności PAŃSTWA (getEmpireFoodReserve(ownerId)) tego ownera, PONIŻEJ którego decideAIEconomySliders (game/ai.ts) przesuwa suwak świeżej żywności (procentRozwoj) w stronę wyżywienia armii. Ta sama wartość na wszystkich trudnościach (zero zapasów = pierwszy sygnał deficytu). PLACEHOLDER do strojenia po playteście.</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>easy=0 … hard=0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Żywność (zapasy państwa, pkt)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ai_suwaki_nadwyzka_zywnosc_prog</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-SUWAKI (Maciej 2026-07-26, C-AI-SUWAKI=A): próg WYRAŹNEJ nadwyżki zapasów Żywności PAŃSTWA (getEmpireFoodReserve(ownerId)), POWYŻEJ którego decideAIEconomySliders (game/ai.ts) wraca suwakiem świeżej żywności (procentRozwoj) w stronę rozwoju miast. Ta sama wartość na wszystkich trudnościach. PLACEHOLDER do strojenia po playteście.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>easy=50 … hard=50</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Żywność (zapasy państwa, pkt)</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ai_suwaki_krok_zywnosc_rozwoj</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-SUWAKI (Maciej 2026-07-26, C-AI-SUWAKI=A): wielkość jednej korekty suwaka świeżej żywności (city.procentRozwoj) w decideAIEconomySliders (game/ai.ts) -- zgodne z krokiem suwaka gracza (HANDEL_PCT_STEP, cities.ts). Ta sama wartość na wszystkich trudnościach. PLACEHOLDER do strojenia po playteście.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>easy=10 … hard=10</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pkt % suwaka procentRozwoj / korekta</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ai_suwaki_krok_praca_nauka</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-SUWAKI (Maciej 2026-07-26, C-AI-SUWAKI=A): wielkość jednej korekty suwaków Pracy (podzialPracy.procentBudynki) i Handlu (podzialHandlu.procentNauka) w decideAIEconomySliders (game/ai.ts) -- wojna przesuwa oba suwaki ku Pracy, pokój ku Nauce. Ta sama wartość na wszystkich trudnościach. PLACEHOLDER do strojenia po playteście.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>easy=10 … hard=10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pkt % suwaka procentBudynki/procentNauka / korekta</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ai_suwaki_min_odstep_tur</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>R-AI-SUWAKI (Maciej 2026-07-26, C-AI-SUWAKI=A): minimalny odstęp między kolejnymi korektami suwaków tego ownera w decideAIEconomySliders (game/ai.ts) -- zabezpieczenie przed oscylacją suwaka tam-i-z-powrotem co turę. Ta sama wartość na wszystkich trudnościach.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>easy=3 … hard=3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>tury</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>economy, magazyny</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>skarbiec_centralny_lokalizacja</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Skarbiec zawsze w stolicy; utrata stolicy zeruje go do 0.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>stolica</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>easy=stolica … hard=stolica</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>miasto</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>economy, magazyny</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -11529,7 +12961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11899,7 +13331,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Mnożnik Mennicy (Handel→Pieniądz). Docelowo ×1,5–×2,0 po upgrade. [PT]</t>
+          <t>NIEUŻYWANE (decyzja Maciej 2026-07-25) — było już martwe wcześniej (żaden kod go nie konsumował). Efekt Mennicy jest teraz w całości opisany przez globalne.mennica_mnoznik_po_walucie (jeden mnożnik na cały Handel netto, aktywny gdy Waluta odkryta ORAZ Mennica zbudowana). Zostawione tylko dla zgodności starych zapisów/narzędzi — kod (economy.ts, turn-economy.ts) go już nie czyta.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11937,20 +13369,20 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Premia Biblioteki do Nauki lokalnie (+50%). [PT — do strojenia]</t>
+          <t>Premia Biblioteki do Nauki miasta. Obniżona +50% → +30% (normalny) decyzją Maciej 2026-07-25 (PYTANIE 75 = C). Powód: dotąd tańsza i wcześniejsza Biblioteka dawała PIĘCIOKROTNIE więcej niż droższa Akademia (+50% vs +10%) — logika była odwrócona. Skalowanie trudnością w konwencji pliku (łatwy ×1,24 / trudny ×0,76). Stackuje ADDYTYWNIE z premią Akademii: Nauka × (1 + premia Biblioteki + premia Akademii) = ×1,50 na normalnym przy obu budynkach (Biblioteka i Akademia to para „w bok" — stoją obok siebie, żadna nie zastępuje drugiej).</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=0.62 … hard=0.38</t>
+          <t>easy=0.37 … hard=0.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ułamek — premia do Nauki miasta (0,30 = +30% Nauki tego miasta na turę)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -11970,25 +13402,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>waluta_mnoznik</t>
+          <t>budynek_akademia_bonus_nauki</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Efekt 1 (Waluta tech): mnoznik na caly handelNetto miasta gdy walutaOdkryta=true (×2 na cala pule Handlu przed podzialem). Dotyczy wszystkich miast automatycznie po wynalezieniu Waluty.</t>
+          <t>Premia Akademii do Nauki miasta. Podniesiona +10% → +20% (normalny) decyzją Maciej 2026-07-25 (PYTANIE 75 = C) i objęta skalowaniem trudnością (łatwy ×1,24 / trudny ×0,76), którego wcześniej nie miała. Powód: Akademia jest droższa i późniejsza od Biblioteki, więc musi dawać wyraźnie mniej niż Biblioteka tylko dlatego, że jest drugim krokiem — a nie pięciokrotnie mniej. Stackuje ADDYTYWNIE z premią Biblioteki: Nauka × (1 + 0,30 + 0,20) = ×1,50 na normalnym.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=2 … hard=2</t>
+          <t>easy=0.25 … hard=0.15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>ułamek — premia do Nauki miasta (0,20 = +20% Nauki tego miasta na turę)</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -12008,12 +13440,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>targowisko_praca_na_pieniadz_mnoznik</t>
+          <t>waluta_mnoznik</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Efekt 2 (Targowisko + Waluta): mnoznik konwersji puli-Pracy (doPuli) na Pieniadz. Aktywny per-miasto gdy maTargowisko=true i walutaOdkryta=true. pieniadzZPracy = floor(doPuli × mnoznik).</t>
+          <t>NIEUŻYWANE (decyzja Maciej 2026-07-25): dawny Efekt 1 'sam tech Waluty odkryty → ×2 na cały Handel netto, bez wymogu Mennicy, jednakowo na wszystkich trudnościach' — ZASTĄPIONY przez globalne.mennica_mnoznik_po_walucie (wymaga Waluty ORAZ Mennicy zbudowanej w mieście; wartość różna per trudność: easy ×2 / normal ×1,5 / hard ×1 czyli brak efektu). Zostawione tylko dla zgodności starych zapisów/narzędzi — kod (economy.ts, turn-economy.ts) go już nie czyta w formule Efektu 1.</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -12046,12 +13478,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>budynek_tartak_przepustowosc</t>
+          <t>targowisko_praca_na_pieniadz_mnoznik</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja Drewno→Deski w Tartaku na turę. [PT]</t>
+          <t>Efekt 2 (Targowisko + Waluta): mnoznik konwersji puli-Pracy (doPuli) na Pieniadz. Aktywny per-miasto gdy maTargowisko=true i walutaOdkryta=true. pieniadzZPracy = floor(doPuli × mnoznik).</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -12059,12 +13491,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=2 … hard=2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>szt/turę</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -12084,20 +13516,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>budynek_cegielnia_przepustowosc</t>
+          <t>budynek_tartak_przepustowosc</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Glina+Drewno)→Cegła w Cegielni na turę. [PT] C-SUROW-CEGLA=A (Maciej 2026-07-24): normal 2→3 (odciążenie cegły wg symulacji bilansu).</t>
+          <t>Maks konwersja Drewno→Deski w Tartaku na turę. [PT]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=3 … hard=1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -12122,20 +13554,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>budynek_huta_przepustowosc</t>
+          <t>budynek_cegielnia_przepustowosc</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Ruda+Drewno)→Brąz w Hucie na turę. [PT]</t>
+          <t>Maks konwersja (Glina+Drewno)→Cegła w Cegielni na turę. [PT] C-SUROW-CEGLA=A (Maciej 2026-07-24): normal 2→3 (odciążenie cegły wg symulacji bilansu).</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -12160,12 +13592,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>budynek_garncarnia_przepustowosc</t>
+          <t>budynek_huta_przepustowosc</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Maks konwersja (Glina+Drewno)→Ceramika w Garncarni na turę. [PT]</t>
+          <t>Maks konwersja (Ruda+Drewno)→Brąz w Odlewni brązu (i tier wyższy łańcucha odlewni) na turę. [PT]</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -12198,12 +13630,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>utrzymanie_budynek</t>
+          <t>budynek_odlewnia_zelaza_przepustowosc</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Koszt utrzymania każdego budynku (niezróżnicowany w v0.1). [PT]</t>
+          <t>Maks konwersja (Ruda żelaza+Drewno)→Żelazo w Odlewni żelaza / Wielka odlewnia na turę. [PT]</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -12211,20 +13643,248 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>easy=2 … hard=0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>budynek_wielka_odlewnia_przepustowosc</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Maks konwersja (Żelazo+Drewno)→Stal w Wielka odlewnia na turę (Maciej 2026-07-27: przeniesione z Wielka Kuźnia). [PT]</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>easy=2 … hard=0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>budynek_garncarnia_przepustowosc</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Maks konwersja (Glina+Drewno)→Ceramika w Garncarni na turę (PYTANIE-84-B5). [PT]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>easy=8 … hard=4</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>szt/turę</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>budynek_spichlerz_zuzywa_ceramika</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-84-B6 (Maciej 2026-07-27): Spichlerz I zużywa Ceramikę ze skarbca państwa co turę; brak surowca → brak bonusów ludności (U-24=B, U-25B).</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>easy=5 … hard=5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ceramika/turę</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>budynek_spichlerz_ii_zuzywa_sol</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-84-B7/U-2 (Maciej 2026-07-27): Spichlerz II zużywa Sól ze skarbca × każdy działający Spichlerz II płacący Sól; brak Soli → brak bonusu wojska (imperium-wide).</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>easy=5 … hard=5</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sól/turę</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>budynek_spichlerz_ii_zuzywa_ceramika</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>PYTANIE-84-B8 (Maciej 2026-07-27): Spichlerz II zużywa Ceramikę ze skarbca co turę (obok Soli); brak Ceramiki → brak bonusu ludności w mieście.</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>easy=5 … hard=5</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ceramika/turę</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts mnozniki</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>econ-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>utrzymanie_budynek</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna stawka utrzymania TYLKO dla budynku bez własnego wpisu `utrzymanie` w buildings.json. Od 2026-07-25 (decyzja właściciela 19=A) silnik czyta utrzymanie z danych każdego budynku (0–5 Pieniądz/turę, zróżnicowane per budynek) — ta wartość NIE nadpisuje ich, jest wyłącznie zabezpieczeniem na wypadek brakującego wpisu. Dziś wszystkie 39 budynków mają własną wartość, więc ta stawka faktycznie się nie stosuje. [PT]</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>easy=1 … hard=2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Pieniądz/turę</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>economy.ts mnozniki</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>econ-params.json</t>
         </is>
@@ -12801,7 +14461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13014,20 +14674,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zdrowie_ceramika</t>
+          <t>zdrowie_laznia_publiczna</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Bonus Zdrowia z Ceramiki/Garncarni (higiena — naczynia do przechowywania żywności). [PT]</t>
+          <t>Bonus Zdrowia z Łaźni publicznej (PYTANIE-85-Q9). Wzrost przez floor(Zdrowie÷10)×1%.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=6 … hard=4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -13052,12 +14712,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zdrowie_male_miasto_bonus</t>
+          <t>zdrowie_ceramika</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>LEGACY — zastąpione przez zdrowie_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+          <t>Bonus Zdrowia z Ceramiki/Garncarni (higiena — naczynia do przechowywania żywności). [PT]</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -13090,22 +14750,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zdrowie_bonus_osiedle_pop</t>
+          <t>zdrowie_male_miasto_bonus</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>D-START-OSIEDLE: bonus Zdrowia malejący pop 1→4 (indeks 0=pop1 … 3=pop4).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2, 1, 1, 0</t>
-        </is>
+          <t>LEGACY — zastąpione przez zdrowie_bonus_osiedle_pop (D-START-OSIEDLE). Fallback gdy brak tablicy.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>easy=[3, 2, 1, 1] … hard=[1, 1, 0, 0]</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -13130,25 +14788,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zdrowie_kara_zagęszczenie</t>
+          <t>zdrowie_bonus_osiedle_pop</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za zagęszczenie — odejmuje 1 pkt Zdrowia za każdy punkt populacji powyżej progu zagęszczenia. [PT]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-1</v>
+          <t>D-START-OSIEDLE: bonus Zdrowia malejący pop 1→4 (indeks 0=pop1 … 3=pop4).</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2, 1, 1, 0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=[3, 2, 1, 1] … hard=[1, 1, 0, 0]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pkt/1 ludności</t>
+          <t>pkt Zdrowia</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -13168,25 +14828,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zdrowie_prog_zagęszczenia</t>
+          <t>zdrowie_kara_zagęszczenie</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Próg zagęszczenia — poniżej tej liczby mieszkańców kara zagęszczenia NIE jest naliczana. [PT — do strojenia]</t>
+          <t>Kara Zdrowia za zagęszczenie — odejmuje 1 pkt Zdrowia za każdy punkt populacji powyżej progu zagęszczenia. [PT]</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ludność</t>
+          <t>pkt/1 ludności</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -13206,25 +14866,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zdrowie_kara_bagno</t>
+          <t>zdrowie_prog_zagęszczenia</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia gdy bagno w promieniu okolicy miasta (choroby, komary). Nie dotyczy lasu. [PT]</t>
+          <t>Próg zagęszczenia — poniżej tej liczby mieszkańców kara zagęszczenia NIE jest naliczana. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=5 … hard=3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pkt Zdrowia</t>
+          <t>ludność</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -13244,20 +14904,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zdrowie_bonus_las</t>
+          <t>zdrowie_kara_bagno</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Bonus Zdrowia gdy w promieniu okolicy miasta jest co najmniej jeden heks z nakładką Las (świeże powietrze, zasoby leśne). [PT]</t>
+          <t>Kara Zdrowia gdy bagno w promieniu okolicy miasta (choroby, komary). Nie dotyczy lasu. [PT]</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -13282,20 +14942,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zdrowie_kara_dzungla</t>
+          <t>zdrowie_bonus_las</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>REZERWA — kara za prawdziwą dżunglę (osobna nakładka klimatyczna). Nakładka Las używa zdrowie_bonus_las, nie tej kary. [PT]</t>
+          <t>Bonus Zdrowia gdy w promieniu okolicy miasta jest co najmniej jeden heks z nakładką Las (świeże powietrze, zasoby leśne). [PT]</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>easy=-0.75 … hard=-1.25</t>
+          <t>easy=2 … hard=0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -13320,12 +14980,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>zdrowie_kara_zanieczyszczenie</t>
+          <t>zdrowie_kara_dzungla</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Piec hutniczy, Cegielnia itp.). Późne epoki. [PT]</t>
+          <t>REZERWA — kara za prawdziwą dżunglę (osobna nakładka klimatyczna). Nakładka Las używa zdrowie_bonus_las, nie tej kary. [PT]</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -13358,20 +15018,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>zdrowie_kara_brak_wody</t>
+          <t>zdrowie_kara_zanieczyszczenie</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Kara Zdrowia gdy miasto nie ma dostępu do świeżej wody (brak Rzeki, Studni ani Akweduktu). [PT — do strojenia]</t>
+          <t>Kara Zdrowia za zanieczyszczenie dymu/przemysłowe (aktywna gdy działają budynki przemysłowe — Piec hutniczy, Cegielnia itp.). Późne epoki. [PT]</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>easy=-1 … hard=-3</t>
+          <t>easy=-0.75 … hard=-1.25</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -13396,25 +15056,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>zdrowie_modyfikator_wzrostu</t>
+          <t>zdrowie_kara_brak_wody</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Modyfikator_Zdrowia = max(0, 1 + Zdrowie × wartość). Np. Zdrowie +4 → ×1,20; Zdrowie −3 → stagnacja. [PT]</t>
+          <t>Kara Zdrowia gdy miasto nie ma dostępu do świeżej wody (brak Rzeki, Studni ani Akweduktu). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.05</v>
+        <v>-2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>easy=0.06 … hard=0.04</t>
+          <t>easy=-1 … hard=-3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>per pkt Zdrowia</t>
+          <t>pkt Zdrowia</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -13434,25 +15094,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>zdrowie_prog_stagnacja</t>
+          <t>zdrowie_modyfikator_wzrostu</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Gdy Zdrowie ≤ tego progu → wzrost populacji zatrzymany (stagnacja). Wzrost odblokowany dopiero gdy Zdrowie &gt; 0. [PT]</t>
+          <t>Modyfikator_Zdrowia = max(0, 1 + Zdrowie × wartość). Np. Zdrowie +4 → ×1,20; Zdrowie −3 → stagnacja. [PT]</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=0 … hard=0</t>
+          <t>easy=0.06 … hard=0.04</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pkt Zdrowia</t>
+          <t>per pkt Zdrowia</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -13472,20 +15132,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>zdrowie_prog_ubytek_populacji</t>
+          <t>zdrowie_prog_stagnacja</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Gdy Zdrowie &lt; tej wartości → możliwy ubytek populacji (co N tur jedna jednostka populacji umiera). [PT — do strojenia]</t>
+          <t>Gdy Zdrowie ≤ tego progu → wzrost populacji zatrzymany (stagnacja). Wzrost odblokowany dopiero gdy Zdrowie &gt; 0. [PT]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=-6 … hard=-4</t>
+          <t>easy=0 … hard=0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -13510,33 +15170,71 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>zdrowie_prog_ubytek_populacji</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Gdy Zdrowie &lt; tej wartości → możliwy ubytek populacji (co N tur jedna jednostka populacji umiera). [PT — do strojenia]</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>easy=-6 … hard=-4</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pkt Zdrowia</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>society.ts zdrowie, wzrost pop</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>society-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>zdrowie_tempo_ubytku</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Co ile tur następuje utrata 1 punktu populacji, gdy Zdrowie &lt; progu ubytku. [PT — do strojenia]</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>easy=4 … hard=2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>tur/utrata</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>society.ts zdrowie, wzrost pop</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>
@@ -13553,7 +15251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -14186,25 +15884,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>szczescie_kara_wysokie_podatki</t>
+          <t>szczescie_siatka_zamoznosc</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Kara Zadowolenia za każdy poziom powyżej bazowej stawki podatkowej (wyższe podatki → gniew). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>-1</v>
+          <t>NOWA SIATKA (Maciej 2026-07-25, decyzja właściciela): co 10 punktów procentowych udziału Zamożności w podziale Daniny netto (suwak handlu miasta) = 1 pkt Szczęścia. Indeks tablicy = dziesiątka udziału: 0=0–9%, 1=10–19%, 2=20–29%, … 8=80–89%, 9=90–100% (suwak sięga 100%, decyzja 72A). Wartości ujemne w indeksach 0–1 (normal) i 0–2 (hard) to KARA za zbyt niski udział Zamożności — nowość, celowa decyzja właściciela. Zastępuje starą, rzadką siatkę (5 progów co 10–20 pkt proc. od 30% wzwyż, bez kary) i stary mechanizm szczescie_kara_wysokie_podatki (usunięty 2026-07-25 — dublował karę poniżej progu bazowego; nowa siatka mierzy to samo zjawisko w sposób ciągły na całym zakresie 0–100%, patrz society-breakdown.ts:luksusHappinessBonus).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-1, 0, 1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>easy=0 … hard=-2</t>
+          <t>easy=[1, 2, 3, 4, 5, 6, 7, 8, 9, 10] … hard=[-2, -1, 0, 1, 2, 3, 4, 5, 6, 7]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pkt/poziom</t>
+          <t>pkt Szczęścia miasta/turę</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -14224,25 +15924,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_30</t>
+          <t>szczescie_prog_bunt</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Bonus Szczęścia gdy udział Zamożność (suwak handlu) ≥ 30% — niskie podatki. [B2-narzedzia-stabilizacji]</t>
+          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>easy=2 … hard=0</t>
+          <t>easy=4 … hard=2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>niezadowoleni</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -14262,25 +15962,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_40</t>
+          <t>szczescie_prog_strajk_produkcja</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność (suwak handlu) ≥ 40%.</t>
+          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>easy=3 … hard=1</t>
+          <t>easy=-1 … hard=-1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -14300,12 +16000,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_50</t>
+          <t>szczescie_prog_bonus_wzrost</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 50%.</t>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -14313,12 +16013,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=2 … hard=4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>zadowoleni</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -14338,25 +16038,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_60</t>
+          <t>szczescie_bonus_wzrost_wartosc</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 60%.</t>
+          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>easy=5 … hard=3</t>
+          <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -14376,12 +16076,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>szczescie_bonus_luksus_70</t>
+          <t>szczescie_prog_bonus_produkcja</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Bonus Sz gdy udział Zamożność ≥ 70% (max suwaka).</t>
+          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -14389,12 +16089,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>easy=6 … hard=4</t>
+          <t>easy=4 … hard=6</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>pkt Sz</t>
+          <t>zadowoleni</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -14414,25 +16114,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>szczescie_prog_bunt</t>
+          <t>szczescie_bonus_produkcja_wartosc</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Gdy liczba niezadowolonych mieszkańców ≥ tej wartości → ryzyko buntu/strajku (brak produkcji z tych mieszkańców). [PT]</t>
+          <t>Mnożnik produkcji (Pracy) przy bardzo wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% Pracy. [PT — do strojenia]</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>easy=4 … hard=2</t>
+          <t>easy=0.12 … hard=0.08</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>niezadowoleni</t>
+          <t>×</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -14441,196 +16141,6 @@
         </is>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>szczescie_prog_strajk_produkcja</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Współczynnik utraty produkcji na każdego niezadowolonego mieszkańca w stanie buntu (strajk → utrata Pracy). [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>easy=-1 … hard=-1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>society.ts szczęście, Porządek</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>szczescie_prog_bonus_wzrost</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do wzrostu populacji (+%). [PT]</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>easy=2 … hard=4</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>zadowoleni</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>society.ts szczęście, Porządek</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>szczescie_bonus_wzrost_wartosc</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Mnożnik wzrostu populacji przy wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% szybciej. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>easy=0.12 … hard=0.08</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>society.ts szczęście, Porządek</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>szczescie_prog_bonus_produkcja</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Gdy liczba zadowolonych mieszkańców ≥ tej wartości → bonus do produkcji (Pracy). [PT]</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>easy=4 … hard=6</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>zadowoleni</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>society.ts szczęście, Porządek</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>society-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>szczescie_bonus_produkcja_wartosc</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Mnożnik produkcji (Pracy) przy bardzo wysokim zadowoleniu (≥ progu). Np. 0,10 = +10% Pracy. [PT — do strojenia]</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>easy=0.12 … hard=0.08</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>society.ts szczęście, Porządek</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
         <is>
           <t>society-params.json</t>
         </is>
